--- a/assets/files/base_scoresheet.xlsx
+++ b/assets/files/base_scoresheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Parth\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE65D033-C594-48DD-83BC-94117C1D0818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1564985-7905-4E77-9DDD-AA3A75F73717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Table 1'!$A$1:$AP$49</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Table 1'!$A$1:$AO$48</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
@@ -1085,7 +1085,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1361,6 +1361,39 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1391,18 +1424,66 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1439,19 +1520,130 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1460,162 +1652,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1639,42 +1675,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1697,9 +1697,9 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>346456</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>209549</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="349250" cy="212090"/>
@@ -1716,7 +1716,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1009396" y="9384029"/>
+          <a:off x="773176" y="9216389"/>
           <a:ext cx="349250" cy="212090"/>
           <a:chOff x="0" y="0"/>
           <a:chExt cx="349250" cy="212090"/>
@@ -1837,9 +1837,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>611058</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>0</xdr:row>
       <xdr:rowOff>284403</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1347282" cy="1245888"/>
@@ -2207,617 +2207,663 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:AO48"/>
+  <dimension ref="A1:AN47"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.44140625" customWidth="1"/>
-    <col min="2" max="2" width="6.21875" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" customWidth="1"/>
-    <col min="4" max="5" width="6.21875" customWidth="1"/>
-    <col min="6" max="6" width="6.44140625" customWidth="1"/>
-    <col min="7" max="8" width="6.21875" customWidth="1"/>
-    <col min="9" max="9" width="6.44140625" customWidth="1"/>
-    <col min="10" max="11" width="6.21875" customWidth="1"/>
-    <col min="12" max="12" width="6.44140625" customWidth="1"/>
-    <col min="13" max="14" width="6.21875" customWidth="1"/>
-    <col min="15" max="15" width="6.44140625" customWidth="1"/>
-    <col min="16" max="17" width="6.21875" customWidth="1"/>
-    <col min="18" max="18" width="6.44140625" customWidth="1"/>
-    <col min="19" max="19" width="6.21875" customWidth="1"/>
-    <col min="20" max="20" width="6.44140625" customWidth="1"/>
-    <col min="21" max="22" width="6.21875" customWidth="1"/>
-    <col min="23" max="23" width="12.6640625" customWidth="1"/>
-    <col min="24" max="24" width="6.21875" customWidth="1"/>
-    <col min="25" max="25" width="6.44140625" customWidth="1"/>
-    <col min="26" max="27" width="6.21875" customWidth="1"/>
-    <col min="28" max="28" width="6.44140625" customWidth="1"/>
-    <col min="29" max="30" width="6.21875" customWidth="1"/>
-    <col min="31" max="31" width="6.44140625" customWidth="1"/>
-    <col min="32" max="33" width="6.21875" customWidth="1"/>
-    <col min="34" max="34" width="6.44140625" customWidth="1"/>
-    <col min="35" max="36" width="6.21875" customWidth="1"/>
-    <col min="37" max="37" width="6.44140625" customWidth="1"/>
-    <col min="38" max="38" width="6.21875" customWidth="1"/>
-    <col min="39" max="39" width="6.44140625" customWidth="1"/>
-    <col min="40" max="41" width="6.21875" customWidth="1"/>
-    <col min="42" max="42" width="3.88671875" customWidth="1"/>
+    <col min="1" max="1" width="6.21875" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" customWidth="1"/>
+    <col min="3" max="4" width="6.21875" customWidth="1"/>
+    <col min="5" max="5" width="6.44140625" customWidth="1"/>
+    <col min="6" max="7" width="6.21875" customWidth="1"/>
+    <col min="8" max="8" width="6.44140625" customWidth="1"/>
+    <col min="9" max="10" width="6.21875" customWidth="1"/>
+    <col min="11" max="11" width="6.44140625" customWidth="1"/>
+    <col min="12" max="13" width="6.21875" customWidth="1"/>
+    <col min="14" max="14" width="6.44140625" customWidth="1"/>
+    <col min="15" max="16" width="6.21875" customWidth="1"/>
+    <col min="17" max="17" width="6.44140625" customWidth="1"/>
+    <col min="18" max="18" width="6.21875" customWidth="1"/>
+    <col min="19" max="19" width="6.44140625" customWidth="1"/>
+    <col min="20" max="21" width="6.21875" customWidth="1"/>
+    <col min="22" max="22" width="12.6640625" customWidth="1"/>
+    <col min="23" max="23" width="6.21875" customWidth="1"/>
+    <col min="24" max="24" width="6.44140625" customWidth="1"/>
+    <col min="25" max="26" width="6.21875" customWidth="1"/>
+    <col min="27" max="27" width="6.44140625" customWidth="1"/>
+    <col min="28" max="29" width="6.21875" customWidth="1"/>
+    <col min="30" max="30" width="6.44140625" customWidth="1"/>
+    <col min="31" max="32" width="6.21875" customWidth="1"/>
+    <col min="33" max="33" width="6.44140625" customWidth="1"/>
+    <col min="34" max="35" width="6.21875" customWidth="1"/>
+    <col min="36" max="36" width="6.44140625" customWidth="1"/>
+    <col min="37" max="37" width="6.21875" customWidth="1"/>
+    <col min="38" max="38" width="6.44140625" customWidth="1"/>
+    <col min="39" max="40" width="6.21875" customWidth="1"/>
+    <col min="41" max="41" width="3.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:41" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="46" t="s">
+    <row r="1" spans="1:40" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="86" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="96" t="s">
         <v>79</v>
       </c>
-      <c r="K2" s="87"/>
-      <c r="L2" s="87"/>
-      <c r="M2" s="87"/>
-      <c r="N2" s="87"/>
-      <c r="O2" s="87"/>
-      <c r="P2" s="87"/>
-      <c r="Q2" s="87"/>
-      <c r="R2" s="87"/>
-      <c r="S2" s="87"/>
-      <c r="T2" s="87"/>
-      <c r="U2" s="87"/>
-      <c r="V2" s="87"/>
-      <c r="W2" s="87"/>
-      <c r="X2" s="87"/>
-      <c r="Y2" s="87"/>
-      <c r="Z2" s="87"/>
-      <c r="AA2" s="87"/>
-      <c r="AB2" s="90" t="s">
+      <c r="J1" s="97"/>
+      <c r="K1" s="97"/>
+      <c r="L1" s="97"/>
+      <c r="M1" s="97"/>
+      <c r="N1" s="97"/>
+      <c r="O1" s="97"/>
+      <c r="P1" s="97"/>
+      <c r="Q1" s="97"/>
+      <c r="R1" s="97"/>
+      <c r="S1" s="97"/>
+      <c r="T1" s="97"/>
+      <c r="U1" s="97"/>
+      <c r="V1" s="97"/>
+      <c r="W1" s="97"/>
+      <c r="X1" s="97"/>
+      <c r="Y1" s="97"/>
+      <c r="Z1" s="97"/>
+      <c r="AA1" s="100" t="s">
         <v>88</v>
       </c>
-      <c r="AC2" s="91"/>
-      <c r="AD2" s="91"/>
-      <c r="AE2" s="91"/>
-      <c r="AF2" s="91"/>
-      <c r="AG2" s="15"/>
-      <c r="AH2" s="22" t="s">
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
+      <c r="AD1" s="101"/>
+      <c r="AE1" s="101"/>
+      <c r="AF1" s="26"/>
+      <c r="AG1" s="49" t="s">
         <v>80</v>
       </c>
-      <c r="AI2" s="23"/>
-      <c r="AJ2" s="23"/>
-      <c r="AK2" s="23"/>
-      <c r="AL2" s="23"/>
-      <c r="AM2" s="23"/>
-      <c r="AN2" s="23"/>
-      <c r="AO2" s="24"/>
-    </row>
-    <row r="3" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="49"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="89"/>
-      <c r="L3" s="89"/>
-      <c r="M3" s="89"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="89"/>
-      <c r="P3" s="89"/>
-      <c r="Q3" s="89"/>
-      <c r="R3" s="89"/>
-      <c r="S3" s="89"/>
-      <c r="T3" s="89"/>
-      <c r="U3" s="89"/>
-      <c r="V3" s="89"/>
-      <c r="W3" s="89"/>
-      <c r="X3" s="89"/>
-      <c r="Y3" s="89"/>
-      <c r="Z3" s="89"/>
-      <c r="AA3" s="89"/>
-      <c r="AB3" s="92"/>
-      <c r="AC3" s="92"/>
-      <c r="AD3" s="92"/>
-      <c r="AE3" s="92"/>
-      <c r="AF3" s="92"/>
-      <c r="AG3" s="17"/>
-      <c r="AH3" s="25" t="s">
+      <c r="AH1" s="50"/>
+      <c r="AI1" s="50"/>
+      <c r="AJ1" s="50"/>
+      <c r="AK1" s="50"/>
+      <c r="AL1" s="50"/>
+      <c r="AM1" s="50"/>
+      <c r="AN1" s="51"/>
+    </row>
+    <row r="2" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="43"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="98"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="99"/>
+      <c r="P2" s="99"/>
+      <c r="Q2" s="99"/>
+      <c r="R2" s="99"/>
+      <c r="S2" s="99"/>
+      <c r="T2" s="99"/>
+      <c r="U2" s="99"/>
+      <c r="V2" s="99"/>
+      <c r="W2" s="99"/>
+      <c r="X2" s="99"/>
+      <c r="Y2" s="99"/>
+      <c r="Z2" s="99"/>
+      <c r="AA2" s="102"/>
+      <c r="AB2" s="102"/>
+      <c r="AC2" s="102"/>
+      <c r="AD2" s="102"/>
+      <c r="AE2" s="102"/>
+      <c r="AF2" s="28"/>
+      <c r="AG2" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="AI3" s="26"/>
-      <c r="AJ3" s="26"/>
-      <c r="AK3" s="26"/>
-      <c r="AL3" s="26"/>
-      <c r="AM3" s="26"/>
-      <c r="AN3" s="26"/>
-      <c r="AO3" s="27"/>
-    </row>
-    <row r="4" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="49"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="28" t="s">
+      <c r="AH2" s="53"/>
+      <c r="AI2" s="53"/>
+      <c r="AJ2" s="53"/>
+      <c r="AK2" s="53"/>
+      <c r="AL2" s="53"/>
+      <c r="AM2" s="53"/>
+      <c r="AN2" s="54"/>
+    </row>
+    <row r="3" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="43"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="K4" s="29"/>
-      <c r="L4" s="29"/>
-      <c r="M4" s="29"/>
-      <c r="N4" s="29"/>
-      <c r="O4" s="29"/>
-      <c r="P4" s="29"/>
-      <c r="Q4" s="29"/>
-      <c r="R4" s="29"/>
-      <c r="S4" s="29"/>
-      <c r="T4" s="29"/>
-      <c r="U4" s="29"/>
-      <c r="V4" s="29"/>
-      <c r="W4" s="29"/>
-      <c r="X4" s="29"/>
-      <c r="Y4" s="29"/>
-      <c r="Z4" s="29"/>
-      <c r="AA4" s="29"/>
-      <c r="AB4" s="29"/>
-      <c r="AC4" s="29"/>
-      <c r="AD4" s="29"/>
-      <c r="AE4" s="29"/>
-      <c r="AF4" s="29"/>
-      <c r="AG4" s="30"/>
-      <c r="AH4" s="18" t="s">
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
+      <c r="L3" s="56"/>
+      <c r="M3" s="56"/>
+      <c r="N3" s="56"/>
+      <c r="O3" s="56"/>
+      <c r="P3" s="56"/>
+      <c r="Q3" s="56"/>
+      <c r="R3" s="56"/>
+      <c r="S3" s="56"/>
+      <c r="T3" s="56"/>
+      <c r="U3" s="56"/>
+      <c r="V3" s="56"/>
+      <c r="W3" s="56"/>
+      <c r="X3" s="56"/>
+      <c r="Y3" s="56"/>
+      <c r="Z3" s="56"/>
+      <c r="AA3" s="56"/>
+      <c r="AB3" s="56"/>
+      <c r="AC3" s="56"/>
+      <c r="AD3" s="56"/>
+      <c r="AE3" s="56"/>
+      <c r="AF3" s="57"/>
+      <c r="AG3" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="AI4" s="19"/>
-      <c r="AJ4" s="20"/>
-      <c r="AK4" s="1" t="s">
+      <c r="AH3" s="17"/>
+      <c r="AI3" s="18"/>
+      <c r="AJ3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="AL4" s="18" t="s">
+      <c r="AK3" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="AM4" s="19"/>
-      <c r="AN4" s="20"/>
-      <c r="AO4" s="1" t="s">
+      <c r="AL3" s="17"/>
+      <c r="AM3" s="18"/>
+      <c r="AN3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="49"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="31"/>
-      <c r="K5" s="32"/>
-      <c r="L5" s="32"/>
-      <c r="M5" s="32"/>
-      <c r="N5" s="32"/>
-      <c r="O5" s="32"/>
-      <c r="P5" s="32"/>
-      <c r="Q5" s="32"/>
-      <c r="R5" s="32"/>
-      <c r="S5" s="32"/>
-      <c r="T5" s="32"/>
-      <c r="U5" s="32"/>
-      <c r="V5" s="32"/>
-      <c r="W5" s="32"/>
-      <c r="X5" s="32"/>
-      <c r="Y5" s="32"/>
-      <c r="Z5" s="32"/>
-      <c r="AA5" s="32"/>
-      <c r="AB5" s="32"/>
-      <c r="AC5" s="32"/>
-      <c r="AD5" s="32"/>
-      <c r="AE5" s="32"/>
-      <c r="AF5" s="32"/>
-      <c r="AG5" s="33"/>
-      <c r="AH5" s="18" t="s">
+    <row r="4" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="43"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="59"/>
+      <c r="L4" s="59"/>
+      <c r="M4" s="59"/>
+      <c r="N4" s="59"/>
+      <c r="O4" s="59"/>
+      <c r="P4" s="59"/>
+      <c r="Q4" s="59"/>
+      <c r="R4" s="59"/>
+      <c r="S4" s="59"/>
+      <c r="T4" s="59"/>
+      <c r="U4" s="59"/>
+      <c r="V4" s="59"/>
+      <c r="W4" s="59"/>
+      <c r="X4" s="59"/>
+      <c r="Y4" s="59"/>
+      <c r="Z4" s="59"/>
+      <c r="AA4" s="59"/>
+      <c r="AB4" s="59"/>
+      <c r="AC4" s="59"/>
+      <c r="AD4" s="59"/>
+      <c r="AE4" s="59"/>
+      <c r="AF4" s="60"/>
+      <c r="AG4" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="AI5" s="19"/>
-      <c r="AJ5" s="20"/>
-      <c r="AK5" s="1" t="s">
+      <c r="AH4" s="17"/>
+      <c r="AI4" s="18"/>
+      <c r="AJ4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AL5" s="18" t="s">
+      <c r="AK4" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="AM5" s="19"/>
-      <c r="AN5" s="20"/>
-      <c r="AO5" s="1" t="s">
+      <c r="AL4" s="17"/>
+      <c r="AM4" s="18"/>
+      <c r="AN4" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="49"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="8" t="s">
+    <row r="5" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="43"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="9"/>
-      <c r="R6" s="9"/>
-      <c r="S6" s="9"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="9"/>
-      <c r="AE6" s="9"/>
-      <c r="AF6" s="9"/>
-      <c r="AG6" s="10"/>
-      <c r="AH6" s="18" t="s">
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="20"/>
+      <c r="U5" s="20"/>
+      <c r="V5" s="20"/>
+      <c r="W5" s="20"/>
+      <c r="X5" s="20"/>
+      <c r="Y5" s="20"/>
+      <c r="Z5" s="20"/>
+      <c r="AA5" s="20"/>
+      <c r="AB5" s="20"/>
+      <c r="AC5" s="20"/>
+      <c r="AD5" s="20"/>
+      <c r="AE5" s="20"/>
+      <c r="AF5" s="21"/>
+      <c r="AG5" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="AI6" s="19"/>
-      <c r="AJ6" s="20"/>
-      <c r="AK6" s="2">
+      <c r="AH5" s="17"/>
+      <c r="AI5" s="18"/>
+      <c r="AJ5" s="2">
         <v>0</v>
       </c>
-      <c r="AL6" s="18" t="s">
+      <c r="AK5" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="AM6" s="19"/>
-      <c r="AN6" s="20"/>
-      <c r="AO6" s="1" t="s">
+      <c r="AL5" s="17"/>
+      <c r="AM5" s="18"/>
+      <c r="AN5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="49"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="50"/>
-      <c r="I7" s="51"/>
-      <c r="J7" s="8" t="s">
+    <row r="6" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="43"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="8" t="s">
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="21"/>
+      <c r="O6" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="9"/>
-      <c r="S7" s="10"/>
-      <c r="T7" s="8" t="s">
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20"/>
+      <c r="R6" s="21"/>
+      <c r="S6" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="U7" s="9"/>
-      <c r="V7" s="9"/>
-      <c r="W7" s="10"/>
-      <c r="X7" s="8" t="s">
+      <c r="T6" s="20"/>
+      <c r="U6" s="20"/>
+      <c r="V6" s="21"/>
+      <c r="W6" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="Y7" s="9"/>
-      <c r="Z7" s="9"/>
-      <c r="AA7" s="10"/>
-      <c r="AB7" s="11" t="s">
+      <c r="X6" s="20"/>
+      <c r="Y6" s="20"/>
+      <c r="Z6" s="21"/>
+      <c r="AA6" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="AC7" s="12"/>
-      <c r="AD7" s="12"/>
-      <c r="AE7" s="13"/>
-      <c r="AF7" s="14" t="s">
+      <c r="AB6" s="23"/>
+      <c r="AC6" s="23"/>
+      <c r="AD6" s="24"/>
+      <c r="AE6" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="AG7" s="15"/>
-      <c r="AH7" s="18" t="s">
+      <c r="AF6" s="26"/>
+      <c r="AG6" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="AI7" s="19"/>
-      <c r="AJ7" s="20"/>
-      <c r="AK7" s="1" t="s">
+      <c r="AH6" s="17"/>
+      <c r="AI6" s="18"/>
+      <c r="AJ6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AL7" s="18" t="s">
+      <c r="AK6" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="AM7" s="19"/>
-      <c r="AN7" s="20"/>
-      <c r="AO7" s="1" t="s">
+      <c r="AL6" s="17"/>
+      <c r="AM6" s="18"/>
+      <c r="AN6" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="49"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="50"/>
-      <c r="E8" s="50"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="8" t="s">
+    <row r="7" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="43"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="21" t="s">
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="12"/>
-      <c r="S8" s="12"/>
-      <c r="T8" s="13"/>
-      <c r="U8" s="11" t="s">
+      <c r="P7" s="23"/>
+      <c r="Q7" s="23"/>
+      <c r="R7" s="23"/>
+      <c r="S7" s="24"/>
+      <c r="T7" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="V8" s="12"/>
-      <c r="W8" s="13"/>
-      <c r="X8" s="11" t="s">
+      <c r="U7" s="23"/>
+      <c r="V7" s="24"/>
+      <c r="W7" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="Y8" s="12"/>
-      <c r="Z8" s="12"/>
-      <c r="AA8" s="13"/>
-      <c r="AB8" s="11" t="s">
+      <c r="X7" s="23"/>
+      <c r="Y7" s="23"/>
+      <c r="Z7" s="24"/>
+      <c r="AA7" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="AC8" s="12"/>
-      <c r="AD8" s="12"/>
-      <c r="AE8" s="13"/>
-      <c r="AF8" s="16"/>
-      <c r="AG8" s="17"/>
-      <c r="AH8" s="18" t="s">
+      <c r="AB7" s="23"/>
+      <c r="AC7" s="23"/>
+      <c r="AD7" s="24"/>
+      <c r="AE7" s="27"/>
+      <c r="AF7" s="28"/>
+      <c r="AG7" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="AI8" s="19"/>
-      <c r="AJ8" s="20"/>
-      <c r="AK8" s="1" t="s">
+      <c r="AH7" s="17"/>
+      <c r="AI7" s="18"/>
+      <c r="AJ7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AL8" s="18" t="s">
+      <c r="AK7" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="AM8" s="19"/>
-      <c r="AN8" s="20"/>
-      <c r="AO8" s="1" t="s">
+      <c r="AL7" s="17"/>
+      <c r="AM7" s="18"/>
+      <c r="AN7" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="52"/>
-      <c r="C9" s="53"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="54"/>
-      <c r="J9" s="34" t="s">
+    <row r="8" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="46"/>
+      <c r="B8" s="47"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="47"/>
+      <c r="E8" s="47"/>
+      <c r="F8" s="47"/>
+      <c r="G8" s="47"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="K9" s="35"/>
-      <c r="L9" s="35"/>
-      <c r="M9" s="35"/>
-      <c r="N9" s="35"/>
-      <c r="O9" s="35"/>
-      <c r="P9" s="35"/>
-      <c r="Q9" s="35"/>
-      <c r="R9" s="35"/>
-      <c r="S9" s="35"/>
-      <c r="T9" s="35"/>
-      <c r="U9" s="36"/>
-      <c r="V9" s="34" t="s">
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31"/>
+      <c r="M8" s="31"/>
+      <c r="N8" s="31"/>
+      <c r="O8" s="31"/>
+      <c r="P8" s="31"/>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="31"/>
+      <c r="S8" s="31"/>
+      <c r="T8" s="32"/>
+      <c r="U8" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="W9" s="35"/>
-      <c r="X9" s="35"/>
-      <c r="Y9" s="35"/>
-      <c r="Z9" s="35"/>
-      <c r="AA9" s="35"/>
-      <c r="AB9" s="35"/>
-      <c r="AC9" s="35"/>
-      <c r="AD9" s="35"/>
-      <c r="AE9" s="35"/>
-      <c r="AF9" s="35"/>
+      <c r="V8" s="31"/>
+      <c r="W8" s="31"/>
+      <c r="X8" s="31"/>
+      <c r="Y8" s="31"/>
+      <c r="Z8" s="31"/>
+      <c r="AA8" s="31"/>
+      <c r="AB8" s="31"/>
+      <c r="AC8" s="31"/>
+      <c r="AD8" s="31"/>
+      <c r="AE8" s="31"/>
+      <c r="AF8" s="32"/>
+      <c r="AG8" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH8" s="17"/>
+      <c r="AI8" s="18"/>
+      <c r="AJ8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK8" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL8" s="17"/>
+      <c r="AM8" s="18"/>
+      <c r="AN8" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:40" ht="12.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="K9" s="36"/>
+      <c r="L9" s="36"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="37"/>
+      <c r="Q9" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="R9" s="36"/>
+      <c r="S9" s="36"/>
+      <c r="T9" s="37"/>
+      <c r="U9" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="V9" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="W9" s="36"/>
+      <c r="X9" s="36"/>
+      <c r="Y9" s="36"/>
+      <c r="Z9" s="36"/>
+      <c r="AA9" s="36"/>
+      <c r="AB9" s="37"/>
+      <c r="AC9" s="3"/>
+      <c r="AD9" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE9" s="36"/>
+      <c r="AF9" s="36"/>
       <c r="AG9" s="36"/>
-      <c r="AH9" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="AI9" s="19"/>
-      <c r="AJ9" s="20"/>
-      <c r="AK9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AL9" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM9" s="19"/>
-      <c r="AN9" s="20"/>
-      <c r="AO9" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="2:41" ht="12.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="L10" s="44"/>
-      <c r="M10" s="44"/>
-      <c r="N10" s="44"/>
-      <c r="O10" s="44"/>
-      <c r="P10" s="44"/>
-      <c r="Q10" s="45"/>
-      <c r="R10" s="43" t="s">
+      <c r="AH9" s="36"/>
+      <c r="AI9" s="36"/>
+      <c r="AJ9" s="37"/>
+      <c r="AK9" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="S10" s="44"/>
-      <c r="T10" s="44"/>
-      <c r="U10" s="45"/>
-      <c r="V10" s="41" t="s">
-        <v>38</v>
-      </c>
-      <c r="W10" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="X10" s="44"/>
-      <c r="Y10" s="44"/>
-      <c r="Z10" s="44"/>
-      <c r="AA10" s="44"/>
-      <c r="AB10" s="44"/>
-      <c r="AC10" s="45"/>
-      <c r="AD10" s="3"/>
-      <c r="AE10" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="AF10" s="44"/>
-      <c r="AG10" s="44"/>
-      <c r="AH10" s="44"/>
-      <c r="AI10" s="44"/>
-      <c r="AJ10" s="44"/>
-      <c r="AK10" s="45"/>
-      <c r="AL10" s="43" t="s">
-        <v>41</v>
-      </c>
-      <c r="AM10" s="44"/>
-      <c r="AN10" s="44"/>
-      <c r="AO10" s="45"/>
-    </row>
-    <row r="11" spans="2:41" ht="12.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="38"/>
-      <c r="C11" s="8" t="s">
+      <c r="AL9" s="36"/>
+      <c r="AM9" s="36"/>
+      <c r="AN9" s="37"/>
+    </row>
+    <row r="10" spans="1:40" ht="12.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="34"/>
+      <c r="B10" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="1" t="s">
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K11" s="43" t="s">
+      <c r="J10" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="L11" s="45"/>
-      <c r="M11" s="43" t="s">
+      <c r="K10" s="37"/>
+      <c r="L10" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="N11" s="45"/>
-      <c r="O11" s="43" t="s">
+      <c r="M10" s="37"/>
+      <c r="N10" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="P11" s="45"/>
-      <c r="Q11" s="1" t="s">
+      <c r="O10" s="37"/>
+      <c r="P10" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="R11" s="1" t="s">
+      <c r="Q10" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="S11" s="1" t="s">
+      <c r="R10" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="T11" s="1" t="s">
+      <c r="S10" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="U11" s="1" t="s">
+      <c r="T10" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="V11" s="42"/>
-      <c r="W11" s="18" t="s">
+      <c r="U10" s="39"/>
+      <c r="V10" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="X11" s="19"/>
-      <c r="Y11" s="19"/>
-      <c r="Z11" s="19"/>
-      <c r="AA11" s="19"/>
-      <c r="AB11" s="19"/>
-      <c r="AC11" s="20"/>
-      <c r="AD11" s="1" t="s">
+      <c r="W10" s="17"/>
+      <c r="X10" s="17"/>
+      <c r="Y10" s="17"/>
+      <c r="Z10" s="17"/>
+      <c r="AA10" s="17"/>
+      <c r="AB10" s="18"/>
+      <c r="AC10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AE11" s="43" t="s">
+      <c r="AD10" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="AF11" s="45"/>
-      <c r="AG11" s="43" t="s">
+      <c r="AE10" s="37"/>
+      <c r="AF10" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="AH11" s="45"/>
-      <c r="AI11" s="43" t="s">
+      <c r="AG10" s="37"/>
+      <c r="AH10" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="AJ11" s="45"/>
-      <c r="AK11" s="1" t="s">
+      <c r="AI10" s="37"/>
+      <c r="AJ10" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AL11" s="1" t="s">
+      <c r="AK10" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AM11" s="1" t="s">
+      <c r="AL10" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AN11" s="1" t="s">
+      <c r="AM10" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AO11" s="1" t="s">
+      <c r="AN10" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="6">
+    <row r="11" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
         <v>1</v>
       </c>
-      <c r="C12" s="55"/>
-      <c r="D12" s="56"/>
-      <c r="E12" s="56"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="56"/>
-      <c r="I12" s="57"/>
+      <c r="B11" s="61"/>
+      <c r="C11" s="62"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
+      <c r="G11" s="62"/>
+      <c r="H11" s="63"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
+      <c r="T11" s="4"/>
+      <c r="U11" s="2">
+        <v>1</v>
+      </c>
+      <c r="V11" s="61"/>
+      <c r="W11" s="62"/>
+      <c r="X11" s="62"/>
+      <c r="Y11" s="62"/>
+      <c r="Z11" s="62"/>
+      <c r="AA11" s="62"/>
+      <c r="AB11" s="63"/>
+      <c r="AC11" s="4"/>
+      <c r="AD11" s="4"/>
+      <c r="AE11" s="4"/>
+      <c r="AF11" s="4"/>
+      <c r="AG11" s="4"/>
+      <c r="AH11" s="4"/>
+      <c r="AI11" s="4"/>
+      <c r="AJ11" s="4"/>
+      <c r="AK11" s="4"/>
+      <c r="AL11" s="4"/>
+      <c r="AM11" s="4"/>
+      <c r="AN11" s="4"/>
+    </row>
+    <row r="12" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>2</v>
+      </c>
+      <c r="B12" s="61"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="62"/>
+      <c r="E12" s="62"/>
+      <c r="F12" s="62"/>
+      <c r="G12" s="62"/>
+      <c r="H12" s="63"/>
+      <c r="I12" s="4"/>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -2829,17 +2875,17 @@
       <c r="R12" s="4"/>
       <c r="S12" s="4"/>
       <c r="T12" s="4"/>
-      <c r="U12" s="4"/>
-      <c r="V12" s="2">
-        <v>1</v>
-      </c>
-      <c r="W12" s="55"/>
-      <c r="X12" s="56"/>
-      <c r="Y12" s="56"/>
-      <c r="Z12" s="56"/>
-      <c r="AA12" s="56"/>
-      <c r="AB12" s="56"/>
-      <c r="AC12" s="57"/>
+      <c r="U12" s="2">
+        <v>2</v>
+      </c>
+      <c r="V12" s="61"/>
+      <c r="W12" s="62"/>
+      <c r="X12" s="62"/>
+      <c r="Y12" s="62"/>
+      <c r="Z12" s="62"/>
+      <c r="AA12" s="62"/>
+      <c r="AB12" s="63"/>
+      <c r="AC12" s="4"/>
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
       <c r="AF12" s="4"/>
@@ -2851,19 +2897,19 @@
       <c r="AL12" s="4"/>
       <c r="AM12" s="4"/>
       <c r="AN12" s="4"/>
-      <c r="AO12" s="4"/>
-    </row>
-    <row r="13" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="6">
-        <v>2</v>
-      </c>
-      <c r="C13" s="55"/>
-      <c r="D13" s="56"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="56"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="57"/>
+    </row>
+    <row r="13" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
+        <v>3</v>
+      </c>
+      <c r="B13" s="61"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="62"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="62"/>
+      <c r="G13" s="62"/>
+      <c r="H13" s="63"/>
+      <c r="I13" s="4"/>
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -2875,17 +2921,17 @@
       <c r="R13" s="4"/>
       <c r="S13" s="4"/>
       <c r="T13" s="4"/>
-      <c r="U13" s="4"/>
-      <c r="V13" s="2">
-        <v>2</v>
-      </c>
-      <c r="W13" s="55"/>
-      <c r="X13" s="56"/>
-      <c r="Y13" s="56"/>
-      <c r="Z13" s="56"/>
-      <c r="AA13" s="56"/>
-      <c r="AB13" s="56"/>
-      <c r="AC13" s="57"/>
+      <c r="U13" s="2">
+        <v>3</v>
+      </c>
+      <c r="V13" s="61"/>
+      <c r="W13" s="62"/>
+      <c r="X13" s="62"/>
+      <c r="Y13" s="62"/>
+      <c r="Z13" s="62"/>
+      <c r="AA13" s="62"/>
+      <c r="AB13" s="63"/>
+      <c r="AC13" s="4"/>
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
       <c r="AF13" s="4"/>
@@ -2897,19 +2943,19 @@
       <c r="AL13" s="4"/>
       <c r="AM13" s="4"/>
       <c r="AN13" s="4"/>
-      <c r="AO13" s="4"/>
-    </row>
-    <row r="14" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="6">
-        <v>3</v>
-      </c>
-      <c r="C14" s="55"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="56"/>
-      <c r="F14" s="56"/>
-      <c r="G14" s="56"/>
-      <c r="H14" s="56"/>
-      <c r="I14" s="57"/>
+    </row>
+    <row r="14" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
+        <v>4</v>
+      </c>
+      <c r="B14" s="61"/>
+      <c r="C14" s="62"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="63"/>
+      <c r="I14" s="4"/>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -2921,17 +2967,17 @@
       <c r="R14" s="4"/>
       <c r="S14" s="4"/>
       <c r="T14" s="4"/>
-      <c r="U14" s="4"/>
-      <c r="V14" s="2">
-        <v>3</v>
-      </c>
-      <c r="W14" s="55"/>
-      <c r="X14" s="56"/>
-      <c r="Y14" s="56"/>
-      <c r="Z14" s="56"/>
-      <c r="AA14" s="56"/>
-      <c r="AB14" s="56"/>
-      <c r="AC14" s="57"/>
+      <c r="U14" s="2">
+        <v>4</v>
+      </c>
+      <c r="V14" s="61"/>
+      <c r="W14" s="62"/>
+      <c r="X14" s="62"/>
+      <c r="Y14" s="62"/>
+      <c r="Z14" s="62"/>
+      <c r="AA14" s="62"/>
+      <c r="AB14" s="63"/>
+      <c r="AC14" s="4"/>
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
       <c r="AF14" s="4"/>
@@ -2943,19 +2989,19 @@
       <c r="AL14" s="4"/>
       <c r="AM14" s="4"/>
       <c r="AN14" s="4"/>
-      <c r="AO14" s="4"/>
-    </row>
-    <row r="15" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="6">
-        <v>4</v>
-      </c>
-      <c r="C15" s="55"/>
-      <c r="D15" s="56"/>
-      <c r="E15" s="56"/>
-      <c r="F15" s="56"/>
-      <c r="G15" s="56"/>
-      <c r="H15" s="56"/>
-      <c r="I15" s="57"/>
+    </row>
+    <row r="15" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <v>5</v>
+      </c>
+      <c r="B15" s="61"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="62"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="62"/>
+      <c r="H15" s="63"/>
+      <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -2967,17 +3013,17 @@
       <c r="R15" s="4"/>
       <c r="S15" s="4"/>
       <c r="T15" s="4"/>
-      <c r="U15" s="4"/>
-      <c r="V15" s="2">
-        <v>4</v>
-      </c>
-      <c r="W15" s="55"/>
-      <c r="X15" s="56"/>
-      <c r="Y15" s="56"/>
-      <c r="Z15" s="56"/>
-      <c r="AA15" s="56"/>
-      <c r="AB15" s="56"/>
-      <c r="AC15" s="57"/>
+      <c r="U15" s="2">
+        <v>5</v>
+      </c>
+      <c r="V15" s="61"/>
+      <c r="W15" s="62"/>
+      <c r="X15" s="62"/>
+      <c r="Y15" s="62"/>
+      <c r="Z15" s="62"/>
+      <c r="AA15" s="62"/>
+      <c r="AB15" s="63"/>
+      <c r="AC15" s="4"/>
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
       <c r="AF15" s="4"/>
@@ -2989,19 +3035,19 @@
       <c r="AL15" s="4"/>
       <c r="AM15" s="4"/>
       <c r="AN15" s="4"/>
-      <c r="AO15" s="4"/>
-    </row>
-    <row r="16" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="6">
-        <v>5</v>
-      </c>
-      <c r="C16" s="55"/>
-      <c r="D16" s="56"/>
-      <c r="E16" s="56"/>
-      <c r="F16" s="56"/>
-      <c r="G16" s="56"/>
-      <c r="H16" s="56"/>
-      <c r="I16" s="57"/>
+    </row>
+    <row r="16" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <v>6</v>
+      </c>
+      <c r="B16" s="61"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="62"/>
+      <c r="E16" s="62"/>
+      <c r="F16" s="62"/>
+      <c r="G16" s="62"/>
+      <c r="H16" s="63"/>
+      <c r="I16" s="4"/>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -3013,17 +3059,17 @@
       <c r="R16" s="4"/>
       <c r="S16" s="4"/>
       <c r="T16" s="4"/>
-      <c r="U16" s="4"/>
-      <c r="V16" s="2">
-        <v>5</v>
-      </c>
-      <c r="W16" s="55"/>
-      <c r="X16" s="56"/>
-      <c r="Y16" s="56"/>
-      <c r="Z16" s="56"/>
-      <c r="AA16" s="56"/>
-      <c r="AB16" s="56"/>
-      <c r="AC16" s="57"/>
+      <c r="U16" s="2">
+        <v>6</v>
+      </c>
+      <c r="V16" s="61"/>
+      <c r="W16" s="62"/>
+      <c r="X16" s="62"/>
+      <c r="Y16" s="62"/>
+      <c r="Z16" s="62"/>
+      <c r="AA16" s="62"/>
+      <c r="AB16" s="63"/>
+      <c r="AC16" s="4"/>
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
       <c r="AF16" s="4"/>
@@ -3035,19 +3081,19 @@
       <c r="AL16" s="4"/>
       <c r="AM16" s="4"/>
       <c r="AN16" s="4"/>
-      <c r="AO16" s="4"/>
-    </row>
-    <row r="17" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="6">
-        <v>6</v>
-      </c>
-      <c r="C17" s="55"/>
-      <c r="D17" s="56"/>
-      <c r="E17" s="56"/>
-      <c r="F17" s="56"/>
-      <c r="G17" s="56"/>
-      <c r="H17" s="56"/>
-      <c r="I17" s="57"/>
+    </row>
+    <row r="17" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>7</v>
+      </c>
+      <c r="B17" s="61"/>
+      <c r="C17" s="62"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="62"/>
+      <c r="F17" s="62"/>
+      <c r="G17" s="62"/>
+      <c r="H17" s="63"/>
+      <c r="I17" s="4"/>
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -3059,17 +3105,17 @@
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
       <c r="T17" s="4"/>
-      <c r="U17" s="4"/>
-      <c r="V17" s="2">
-        <v>6</v>
-      </c>
-      <c r="W17" s="55"/>
-      <c r="X17" s="56"/>
-      <c r="Y17" s="56"/>
-      <c r="Z17" s="56"/>
-      <c r="AA17" s="56"/>
-      <c r="AB17" s="56"/>
-      <c r="AC17" s="57"/>
+      <c r="U17" s="2">
+        <v>7</v>
+      </c>
+      <c r="V17" s="61"/>
+      <c r="W17" s="62"/>
+      <c r="X17" s="62"/>
+      <c r="Y17" s="62"/>
+      <c r="Z17" s="62"/>
+      <c r="AA17" s="62"/>
+      <c r="AB17" s="63"/>
+      <c r="AC17" s="4"/>
       <c r="AD17" s="4"/>
       <c r="AE17" s="4"/>
       <c r="AF17" s="4"/>
@@ -3081,19 +3127,19 @@
       <c r="AL17" s="4"/>
       <c r="AM17" s="4"/>
       <c r="AN17" s="4"/>
-      <c r="AO17" s="4"/>
-    </row>
-    <row r="18" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="6">
-        <v>7</v>
-      </c>
-      <c r="C18" s="55"/>
-      <c r="D18" s="56"/>
-      <c r="E18" s="56"/>
-      <c r="F18" s="56"/>
-      <c r="G18" s="56"/>
-      <c r="H18" s="56"/>
-      <c r="I18" s="57"/>
+    </row>
+    <row r="18" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
+        <v>8</v>
+      </c>
+      <c r="B18" s="61"/>
+      <c r="C18" s="62"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="62"/>
+      <c r="F18" s="62"/>
+      <c r="G18" s="62"/>
+      <c r="H18" s="63"/>
+      <c r="I18" s="4"/>
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -3105,17 +3151,17 @@
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
       <c r="T18" s="4"/>
-      <c r="U18" s="4"/>
-      <c r="V18" s="2">
-        <v>7</v>
-      </c>
-      <c r="W18" s="55"/>
-      <c r="X18" s="56"/>
-      <c r="Y18" s="56"/>
-      <c r="Z18" s="56"/>
-      <c r="AA18" s="56"/>
-      <c r="AB18" s="56"/>
-      <c r="AC18" s="57"/>
+      <c r="U18" s="2">
+        <v>8</v>
+      </c>
+      <c r="V18" s="61"/>
+      <c r="W18" s="62"/>
+      <c r="X18" s="62"/>
+      <c r="Y18" s="62"/>
+      <c r="Z18" s="62"/>
+      <c r="AA18" s="62"/>
+      <c r="AB18" s="63"/>
+      <c r="AC18" s="4"/>
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
       <c r="AF18" s="4"/>
@@ -3127,19 +3173,19 @@
       <c r="AL18" s="4"/>
       <c r="AM18" s="4"/>
       <c r="AN18" s="4"/>
-      <c r="AO18" s="4"/>
-    </row>
-    <row r="19" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="6">
-        <v>8</v>
-      </c>
-      <c r="C19" s="55"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="56"/>
-      <c r="F19" s="56"/>
-      <c r="G19" s="56"/>
-      <c r="H19" s="56"/>
-      <c r="I19" s="57"/>
+    </row>
+    <row r="19" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <v>9</v>
+      </c>
+      <c r="B19" s="61"/>
+      <c r="C19" s="62"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="62"/>
+      <c r="F19" s="62"/>
+      <c r="G19" s="62"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="4"/>
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -3151,17 +3197,17 @@
       <c r="R19" s="4"/>
       <c r="S19" s="4"/>
       <c r="T19" s="4"/>
-      <c r="U19" s="4"/>
-      <c r="V19" s="2">
-        <v>8</v>
-      </c>
-      <c r="W19" s="55"/>
-      <c r="X19" s="56"/>
-      <c r="Y19" s="56"/>
-      <c r="Z19" s="56"/>
-      <c r="AA19" s="56"/>
-      <c r="AB19" s="56"/>
-      <c r="AC19" s="57"/>
+      <c r="U19" s="2">
+        <v>9</v>
+      </c>
+      <c r="V19" s="61"/>
+      <c r="W19" s="62"/>
+      <c r="X19" s="62"/>
+      <c r="Y19" s="62"/>
+      <c r="Z19" s="62"/>
+      <c r="AA19" s="62"/>
+      <c r="AB19" s="63"/>
+      <c r="AC19" s="4"/>
       <c r="AD19" s="4"/>
       <c r="AE19" s="4"/>
       <c r="AF19" s="4"/>
@@ -3173,19 +3219,19 @@
       <c r="AL19" s="4"/>
       <c r="AM19" s="4"/>
       <c r="AN19" s="4"/>
-      <c r="AO19" s="4"/>
-    </row>
-    <row r="20" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="6">
-        <v>9</v>
-      </c>
-      <c r="C20" s="55"/>
-      <c r="D20" s="56"/>
-      <c r="E20" s="56"/>
-      <c r="F20" s="56"/>
-      <c r="G20" s="56"/>
-      <c r="H20" s="56"/>
-      <c r="I20" s="57"/>
+    </row>
+    <row r="20" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
+        <v>10</v>
+      </c>
+      <c r="B20" s="61"/>
+      <c r="C20" s="62"/>
+      <c r="D20" s="62"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="62"/>
+      <c r="H20" s="63"/>
+      <c r="I20" s="4"/>
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -3197,17 +3243,17 @@
       <c r="R20" s="4"/>
       <c r="S20" s="4"/>
       <c r="T20" s="4"/>
-      <c r="U20" s="4"/>
-      <c r="V20" s="2">
-        <v>9</v>
-      </c>
-      <c r="W20" s="55"/>
-      <c r="X20" s="56"/>
-      <c r="Y20" s="56"/>
-      <c r="Z20" s="56"/>
-      <c r="AA20" s="56"/>
-      <c r="AB20" s="56"/>
-      <c r="AC20" s="57"/>
+      <c r="U20" s="2">
+        <v>10</v>
+      </c>
+      <c r="V20" s="61"/>
+      <c r="W20" s="62"/>
+      <c r="X20" s="62"/>
+      <c r="Y20" s="62"/>
+      <c r="Z20" s="62"/>
+      <c r="AA20" s="62"/>
+      <c r="AB20" s="63"/>
+      <c r="AC20" s="4"/>
       <c r="AD20" s="4"/>
       <c r="AE20" s="4"/>
       <c r="AF20" s="4"/>
@@ -3219,19 +3265,19 @@
       <c r="AL20" s="4"/>
       <c r="AM20" s="4"/>
       <c r="AN20" s="4"/>
-      <c r="AO20" s="4"/>
-    </row>
-    <row r="21" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="6">
-        <v>10</v>
-      </c>
-      <c r="C21" s="55"/>
-      <c r="D21" s="56"/>
-      <c r="E21" s="56"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="56"/>
-      <c r="I21" s="57"/>
+    </row>
+    <row r="21" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
+        <v>11</v>
+      </c>
+      <c r="B21" s="61"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="62"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="62"/>
+      <c r="H21" s="63"/>
+      <c r="I21" s="4"/>
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -3243,17 +3289,17 @@
       <c r="R21" s="4"/>
       <c r="S21" s="4"/>
       <c r="T21" s="4"/>
-      <c r="U21" s="4"/>
-      <c r="V21" s="2">
-        <v>10</v>
-      </c>
-      <c r="W21" s="55"/>
-      <c r="X21" s="56"/>
-      <c r="Y21" s="56"/>
-      <c r="Z21" s="56"/>
-      <c r="AA21" s="56"/>
-      <c r="AB21" s="56"/>
-      <c r="AC21" s="57"/>
+      <c r="U21" s="2">
+        <v>11</v>
+      </c>
+      <c r="V21" s="61"/>
+      <c r="W21" s="62"/>
+      <c r="X21" s="62"/>
+      <c r="Y21" s="62"/>
+      <c r="Z21" s="62"/>
+      <c r="AA21" s="62"/>
+      <c r="AB21" s="63"/>
+      <c r="AC21" s="4"/>
       <c r="AD21" s="4"/>
       <c r="AE21" s="4"/>
       <c r="AF21" s="4"/>
@@ -3265,19 +3311,19 @@
       <c r="AL21" s="4"/>
       <c r="AM21" s="4"/>
       <c r="AN21" s="4"/>
-      <c r="AO21" s="4"/>
-    </row>
-    <row r="22" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="6">
-        <v>11</v>
-      </c>
-      <c r="C22" s="55"/>
-      <c r="D22" s="56"/>
-      <c r="E22" s="56"/>
-      <c r="F22" s="56"/>
-      <c r="G22" s="56"/>
-      <c r="H22" s="56"/>
-      <c r="I22" s="57"/>
+    </row>
+    <row r="22" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
+        <v>12</v>
+      </c>
+      <c r="B22" s="61"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="63"/>
+      <c r="I22" s="4"/>
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -3289,17 +3335,17 @@
       <c r="R22" s="4"/>
       <c r="S22" s="4"/>
       <c r="T22" s="4"/>
-      <c r="U22" s="4"/>
-      <c r="V22" s="2">
-        <v>11</v>
-      </c>
-      <c r="W22" s="55"/>
-      <c r="X22" s="56"/>
-      <c r="Y22" s="56"/>
-      <c r="Z22" s="56"/>
-      <c r="AA22" s="56"/>
-      <c r="AB22" s="56"/>
-      <c r="AC22" s="57"/>
+      <c r="U22" s="2">
+        <v>12</v>
+      </c>
+      <c r="V22" s="61"/>
+      <c r="W22" s="62"/>
+      <c r="X22" s="62"/>
+      <c r="Y22" s="62"/>
+      <c r="Z22" s="62"/>
+      <c r="AA22" s="62"/>
+      <c r="AB22" s="63"/>
+      <c r="AC22" s="4"/>
       <c r="AD22" s="4"/>
       <c r="AE22" s="4"/>
       <c r="AF22" s="4"/>
@@ -3311,19 +3357,19 @@
       <c r="AL22" s="4"/>
       <c r="AM22" s="4"/>
       <c r="AN22" s="4"/>
-      <c r="AO22" s="4"/>
-    </row>
-    <row r="23" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="6">
-        <v>12</v>
-      </c>
-      <c r="C23" s="55"/>
-      <c r="D23" s="56"/>
-      <c r="E23" s="56"/>
-      <c r="F23" s="56"/>
-      <c r="G23" s="56"/>
-      <c r="H23" s="56"/>
-      <c r="I23" s="57"/>
+    </row>
+    <row r="23" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="6">
+        <v>13</v>
+      </c>
+      <c r="B23" s="61"/>
+      <c r="C23" s="62"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="62"/>
+      <c r="F23" s="62"/>
+      <c r="G23" s="62"/>
+      <c r="H23" s="63"/>
+      <c r="I23" s="4"/>
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -3335,17 +3381,17 @@
       <c r="R23" s="4"/>
       <c r="S23" s="4"/>
       <c r="T23" s="4"/>
-      <c r="U23" s="4"/>
-      <c r="V23" s="2">
-        <v>12</v>
-      </c>
-      <c r="W23" s="55"/>
-      <c r="X23" s="56"/>
-      <c r="Y23" s="56"/>
-      <c r="Z23" s="56"/>
-      <c r="AA23" s="56"/>
-      <c r="AB23" s="56"/>
-      <c r="AC23" s="57"/>
+      <c r="U23" s="2">
+        <v>13</v>
+      </c>
+      <c r="V23" s="61"/>
+      <c r="W23" s="62"/>
+      <c r="X23" s="62"/>
+      <c r="Y23" s="62"/>
+      <c r="Z23" s="62"/>
+      <c r="AA23" s="62"/>
+      <c r="AB23" s="63"/>
+      <c r="AC23" s="4"/>
       <c r="AD23" s="4"/>
       <c r="AE23" s="4"/>
       <c r="AF23" s="4"/>
@@ -3357,19 +3403,19 @@
       <c r="AL23" s="4"/>
       <c r="AM23" s="4"/>
       <c r="AN23" s="4"/>
-      <c r="AO23" s="4"/>
-    </row>
-    <row r="24" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="6">
-        <v>13</v>
-      </c>
-      <c r="C24" s="55"/>
-      <c r="D24" s="56"/>
-      <c r="E24" s="56"/>
-      <c r="F24" s="56"/>
-      <c r="G24" s="56"/>
-      <c r="H24" s="56"/>
-      <c r="I24" s="57"/>
+    </row>
+    <row r="24" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
+        <v>14</v>
+      </c>
+      <c r="B24" s="61"/>
+      <c r="C24" s="62"/>
+      <c r="D24" s="62"/>
+      <c r="E24" s="62"/>
+      <c r="F24" s="62"/>
+      <c r="G24" s="62"/>
+      <c r="H24" s="63"/>
+      <c r="I24" s="4"/>
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -3381,17 +3427,17 @@
       <c r="R24" s="4"/>
       <c r="S24" s="4"/>
       <c r="T24" s="4"/>
-      <c r="U24" s="4"/>
-      <c r="V24" s="2">
-        <v>13</v>
-      </c>
-      <c r="W24" s="55"/>
-      <c r="X24" s="56"/>
-      <c r="Y24" s="56"/>
-      <c r="Z24" s="56"/>
-      <c r="AA24" s="56"/>
-      <c r="AB24" s="56"/>
-      <c r="AC24" s="57"/>
+      <c r="U24" s="2">
+        <v>14</v>
+      </c>
+      <c r="V24" s="61"/>
+      <c r="W24" s="62"/>
+      <c r="X24" s="62"/>
+      <c r="Y24" s="62"/>
+      <c r="Z24" s="62"/>
+      <c r="AA24" s="62"/>
+      <c r="AB24" s="63"/>
+      <c r="AC24" s="4"/>
       <c r="AD24" s="4"/>
       <c r="AE24" s="4"/>
       <c r="AF24" s="4"/>
@@ -3403,19 +3449,19 @@
       <c r="AL24" s="4"/>
       <c r="AM24" s="4"/>
       <c r="AN24" s="4"/>
-      <c r="AO24" s="4"/>
-    </row>
-    <row r="25" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="6">
-        <v>14</v>
-      </c>
-      <c r="C25" s="55"/>
-      <c r="D25" s="56"/>
-      <c r="E25" s="56"/>
-      <c r="F25" s="56"/>
-      <c r="G25" s="56"/>
-      <c r="H25" s="56"/>
-      <c r="I25" s="57"/>
+    </row>
+    <row r="25" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="6">
+        <v>15</v>
+      </c>
+      <c r="B25" s="61"/>
+      <c r="C25" s="62"/>
+      <c r="D25" s="62"/>
+      <c r="E25" s="62"/>
+      <c r="F25" s="62"/>
+      <c r="G25" s="62"/>
+      <c r="H25" s="63"/>
+      <c r="I25" s="4"/>
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -3427,17 +3473,17 @@
       <c r="R25" s="4"/>
       <c r="S25" s="4"/>
       <c r="T25" s="4"/>
-      <c r="U25" s="4"/>
-      <c r="V25" s="2">
-        <v>14</v>
-      </c>
-      <c r="W25" s="55"/>
-      <c r="X25" s="56"/>
-      <c r="Y25" s="56"/>
-      <c r="Z25" s="56"/>
-      <c r="AA25" s="56"/>
-      <c r="AB25" s="56"/>
-      <c r="AC25" s="57"/>
+      <c r="U25" s="2">
+        <v>15</v>
+      </c>
+      <c r="V25" s="61"/>
+      <c r="W25" s="62"/>
+      <c r="X25" s="62"/>
+      <c r="Y25" s="62"/>
+      <c r="Z25" s="62"/>
+      <c r="AA25" s="62"/>
+      <c r="AB25" s="63"/>
+      <c r="AC25" s="4"/>
       <c r="AD25" s="4"/>
       <c r="AE25" s="4"/>
       <c r="AF25" s="4"/>
@@ -3449,115 +3495,115 @@
       <c r="AL25" s="4"/>
       <c r="AM25" s="4"/>
       <c r="AN25" s="4"/>
-      <c r="AO25" s="4"/>
-    </row>
-    <row r="26" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="6">
-        <v>15</v>
-      </c>
-      <c r="C26" s="55"/>
-      <c r="D26" s="56"/>
-      <c r="E26" s="56"/>
-      <c r="F26" s="56"/>
-      <c r="G26" s="56"/>
-      <c r="H26" s="56"/>
-      <c r="I26" s="57"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4"/>
-      <c r="M26" s="4"/>
-      <c r="N26" s="4"/>
-      <c r="O26" s="4"/>
-      <c r="P26" s="4"/>
-      <c r="Q26" s="4"/>
-      <c r="R26" s="4"/>
-      <c r="S26" s="4"/>
-      <c r="T26" s="4"/>
-      <c r="U26" s="4"/>
-      <c r="V26" s="2">
-        <v>15</v>
-      </c>
-      <c r="W26" s="55"/>
-      <c r="X26" s="56"/>
-      <c r="Y26" s="56"/>
-      <c r="Z26" s="56"/>
-      <c r="AA26" s="56"/>
-      <c r="AB26" s="56"/>
-      <c r="AC26" s="57"/>
-      <c r="AD26" s="4"/>
-      <c r="AE26" s="4"/>
-      <c r="AF26" s="4"/>
-      <c r="AG26" s="4"/>
-      <c r="AH26" s="4"/>
-      <c r="AI26" s="4"/>
-      <c r="AJ26" s="4"/>
-      <c r="AK26" s="4"/>
-      <c r="AL26" s="4"/>
-      <c r="AM26" s="4"/>
-      <c r="AN26" s="4"/>
-      <c r="AO26" s="4"/>
-    </row>
-    <row r="27" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="8" t="s">
+    </row>
+    <row r="26" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="10"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="K26" s="36"/>
+      <c r="L26" s="36"/>
+      <c r="M26" s="36"/>
+      <c r="N26" s="36"/>
+      <c r="O26" s="36"/>
+      <c r="P26" s="36"/>
+      <c r="Q26" s="36"/>
+      <c r="R26" s="36"/>
+      <c r="S26" s="36"/>
+      <c r="T26" s="37"/>
+      <c r="U26" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="V26" s="17"/>
+      <c r="W26" s="17"/>
+      <c r="X26" s="17"/>
+      <c r="Y26" s="17"/>
+      <c r="Z26" s="17"/>
+      <c r="AA26" s="17"/>
+      <c r="AB26" s="18"/>
+      <c r="AC26" s="4"/>
+      <c r="AD26" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE26" s="36"/>
+      <c r="AF26" s="36"/>
+      <c r="AG26" s="36"/>
+      <c r="AH26" s="36"/>
+      <c r="AI26" s="36"/>
+      <c r="AJ26" s="36"/>
+      <c r="AK26" s="36"/>
+      <c r="AL26" s="36"/>
+      <c r="AM26" s="36"/>
+      <c r="AN26" s="37"/>
+    </row>
+    <row r="27" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="4"/>
       <c r="J27" s="4"/>
-      <c r="K27" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="L27" s="44"/>
-      <c r="M27" s="44"/>
-      <c r="N27" s="44"/>
-      <c r="O27" s="44"/>
-      <c r="P27" s="44"/>
-      <c r="Q27" s="44"/>
-      <c r="R27" s="44"/>
-      <c r="S27" s="44"/>
-      <c r="T27" s="44"/>
-      <c r="U27" s="45"/>
-      <c r="V27" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="W27" s="19"/>
-      <c r="X27" s="19"/>
-      <c r="Y27" s="19"/>
-      <c r="Z27" s="19"/>
-      <c r="AA27" s="19"/>
-      <c r="AB27" s="19"/>
-      <c r="AC27" s="20"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="4"/>
+      <c r="N27" s="4"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="4"/>
+      <c r="Q27" s="4"/>
+      <c r="R27" s="4"/>
+      <c r="S27" s="4"/>
+      <c r="T27" s="4"/>
+      <c r="U27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="V27" s="17"/>
+      <c r="W27" s="17"/>
+      <c r="X27" s="17"/>
+      <c r="Y27" s="17"/>
+      <c r="Z27" s="17"/>
+      <c r="AA27" s="17"/>
+      <c r="AB27" s="18"/>
+      <c r="AC27" s="4"/>
       <c r="AD27" s="4"/>
-      <c r="AE27" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF27" s="44"/>
-      <c r="AG27" s="44"/>
-      <c r="AH27" s="44"/>
-      <c r="AI27" s="44"/>
-      <c r="AJ27" s="44"/>
-      <c r="AK27" s="44"/>
-      <c r="AL27" s="44"/>
-      <c r="AM27" s="44"/>
-      <c r="AN27" s="44"/>
-      <c r="AO27" s="45"/>
-    </row>
-    <row r="28" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="10"/>
+      <c r="AE27" s="4"/>
+      <c r="AF27" s="4"/>
+      <c r="AG27" s="4"/>
+      <c r="AH27" s="4"/>
+      <c r="AI27" s="4"/>
+      <c r="AJ27" s="4"/>
+      <c r="AK27" s="4"/>
+      <c r="AL27" s="4"/>
+      <c r="AM27" s="4"/>
+      <c r="AN27" s="4"/>
+    </row>
+    <row r="28" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="4"/>
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -3569,17 +3615,17 @@
       <c r="R28" s="4"/>
       <c r="S28" s="4"/>
       <c r="T28" s="4"/>
-      <c r="U28" s="4"/>
-      <c r="V28" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="W28" s="19"/>
-      <c r="X28" s="19"/>
-      <c r="Y28" s="19"/>
-      <c r="Z28" s="19"/>
-      <c r="AA28" s="19"/>
-      <c r="AB28" s="19"/>
-      <c r="AC28" s="20"/>
+      <c r="U28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="V28" s="17"/>
+      <c r="W28" s="17"/>
+      <c r="X28" s="17"/>
+      <c r="Y28" s="17"/>
+      <c r="Z28" s="17"/>
+      <c r="AA28" s="17"/>
+      <c r="AB28" s="18"/>
+      <c r="AC28" s="4"/>
       <c r="AD28" s="4"/>
       <c r="AE28" s="4"/>
       <c r="AF28" s="4"/>
@@ -3591,309 +3637,309 @@
       <c r="AL28" s="4"/>
       <c r="AM28" s="4"/>
       <c r="AN28" s="4"/>
-      <c r="AO28" s="4"/>
-    </row>
-    <row r="29" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="4"/>
-      <c r="M29" s="4"/>
-      <c r="N29" s="4"/>
-      <c r="O29" s="4"/>
-      <c r="P29" s="4"/>
-      <c r="Q29" s="4"/>
-      <c r="R29" s="4"/>
-      <c r="S29" s="4"/>
-      <c r="T29" s="4"/>
-      <c r="U29" s="4"/>
-      <c r="V29" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="W29" s="19"/>
-      <c r="X29" s="19"/>
-      <c r="Y29" s="19"/>
-      <c r="Z29" s="19"/>
-      <c r="AA29" s="19"/>
-      <c r="AB29" s="19"/>
-      <c r="AC29" s="20"/>
-      <c r="AD29" s="4"/>
-      <c r="AE29" s="4"/>
-      <c r="AF29" s="4"/>
-      <c r="AG29" s="4"/>
-      <c r="AH29" s="4"/>
-      <c r="AI29" s="4"/>
-      <c r="AJ29" s="4"/>
-      <c r="AK29" s="4"/>
-      <c r="AL29" s="4"/>
-      <c r="AM29" s="4"/>
-      <c r="AN29" s="4"/>
-      <c r="AO29" s="4"/>
-    </row>
-    <row r="30" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="11" t="s">
+    </row>
+    <row r="29" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="C30" s="13"/>
-      <c r="D30" s="11" t="s">
+      <c r="B29" s="24"/>
+      <c r="C29" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="E30" s="12"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="11" t="s">
+      <c r="D29" s="23"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="H30" s="12"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="11" t="s">
+      <c r="G29" s="23"/>
+      <c r="H29" s="24"/>
+      <c r="I29" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="K30" s="13"/>
-      <c r="L30" s="11" t="s">
+      <c r="J29" s="24"/>
+      <c r="K29" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="M30" s="12"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="12"/>
-      <c r="P30" s="12"/>
-      <c r="Q30" s="12"/>
-      <c r="R30" s="12"/>
-      <c r="S30" s="12"/>
-      <c r="T30" s="12"/>
-      <c r="U30" s="13"/>
-      <c r="V30" s="11" t="s">
+      <c r="L29" s="23"/>
+      <c r="M29" s="23"/>
+      <c r="N29" s="23"/>
+      <c r="O29" s="23"/>
+      <c r="P29" s="23"/>
+      <c r="Q29" s="23"/>
+      <c r="R29" s="23"/>
+      <c r="S29" s="23"/>
+      <c r="T29" s="24"/>
+      <c r="U29" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="W30" s="13"/>
-      <c r="X30" s="11" t="s">
+      <c r="V29" s="24"/>
+      <c r="W29" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="Y30" s="12"/>
-      <c r="Z30" s="13"/>
-      <c r="AA30" s="11" t="s">
+      <c r="X29" s="23"/>
+      <c r="Y29" s="24"/>
+      <c r="Z29" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="AB30" s="12"/>
-      <c r="AC30" s="13"/>
-      <c r="AD30" s="11" t="s">
+      <c r="AA29" s="23"/>
+      <c r="AB29" s="24"/>
+      <c r="AC29" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="AE30" s="13"/>
-      <c r="AF30" s="11" t="s">
+      <c r="AD29" s="24"/>
+      <c r="AE29" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="AG30" s="12"/>
-      <c r="AH30" s="12"/>
-      <c r="AI30" s="12"/>
-      <c r="AJ30" s="12"/>
-      <c r="AK30" s="12"/>
-      <c r="AL30" s="12"/>
-      <c r="AM30" s="12"/>
-      <c r="AN30" s="12"/>
-      <c r="AO30" s="13"/>
-    </row>
-    <row r="31" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="58"/>
-      <c r="C31" s="59"/>
-      <c r="D31" s="58"/>
-      <c r="E31" s="62"/>
-      <c r="F31" s="59"/>
-      <c r="G31" s="58"/>
-      <c r="H31" s="62"/>
-      <c r="I31" s="59"/>
-      <c r="J31" s="58"/>
-      <c r="K31" s="59"/>
-      <c r="L31" s="64" t="s">
+      <c r="AF29" s="23"/>
+      <c r="AG29" s="23"/>
+      <c r="AH29" s="23"/>
+      <c r="AI29" s="23"/>
+      <c r="AJ29" s="23"/>
+      <c r="AK29" s="23"/>
+      <c r="AL29" s="23"/>
+      <c r="AM29" s="23"/>
+      <c r="AN29" s="24"/>
+    </row>
+    <row r="30" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="67"/>
+      <c r="B30" s="68"/>
+      <c r="C30" s="67"/>
+      <c r="D30" s="73"/>
+      <c r="E30" s="68"/>
+      <c r="F30" s="67"/>
+      <c r="G30" s="73"/>
+      <c r="H30" s="68"/>
+      <c r="I30" s="67"/>
+      <c r="J30" s="68"/>
+      <c r="K30" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="M31" s="65"/>
-      <c r="N31" s="66"/>
-      <c r="O31" s="64" t="s">
+      <c r="L30" s="65"/>
+      <c r="M30" s="66"/>
+      <c r="N30" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="P31" s="65"/>
-      <c r="Q31" s="66"/>
-      <c r="R31" s="64" t="s">
+      <c r="O30" s="65"/>
+      <c r="P30" s="66"/>
+      <c r="Q30" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="S31" s="65"/>
-      <c r="T31" s="66"/>
-      <c r="U31" s="7" t="s">
+      <c r="R30" s="65"/>
+      <c r="S30" s="66"/>
+      <c r="T30" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="V31" s="58"/>
-      <c r="W31" s="59"/>
-      <c r="X31" s="58"/>
-      <c r="Y31" s="62"/>
-      <c r="Z31" s="59"/>
-      <c r="AA31" s="58"/>
-      <c r="AB31" s="62"/>
-      <c r="AC31" s="59"/>
-      <c r="AD31" s="58"/>
-      <c r="AE31" s="59"/>
-      <c r="AF31" s="64" t="s">
+      <c r="U30" s="67"/>
+      <c r="V30" s="68"/>
+      <c r="W30" s="67"/>
+      <c r="X30" s="73"/>
+      <c r="Y30" s="68"/>
+      <c r="Z30" s="67"/>
+      <c r="AA30" s="73"/>
+      <c r="AB30" s="68"/>
+      <c r="AC30" s="67"/>
+      <c r="AD30" s="68"/>
+      <c r="AE30" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="AG31" s="65"/>
-      <c r="AH31" s="66"/>
-      <c r="AI31" s="64" t="s">
+      <c r="AF30" s="65"/>
+      <c r="AG30" s="66"/>
+      <c r="AH30" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="AJ31" s="65"/>
-      <c r="AK31" s="66"/>
-      <c r="AL31" s="64" t="s">
+      <c r="AI30" s="65"/>
+      <c r="AJ30" s="66"/>
+      <c r="AK30" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="AM31" s="65"/>
-      <c r="AN31" s="66"/>
-      <c r="AO31" s="7" t="s">
+      <c r="AL30" s="65"/>
+      <c r="AM30" s="66"/>
+      <c r="AN30" s="7" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="2:41" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="105"/>
-      <c r="C32" s="106"/>
-      <c r="D32" s="105"/>
-      <c r="E32" s="107"/>
-      <c r="F32" s="106"/>
-      <c r="G32" s="105"/>
-      <c r="H32" s="107"/>
-      <c r="I32" s="106"/>
-      <c r="J32" s="105"/>
-      <c r="K32" s="107"/>
-      <c r="L32" s="110"/>
-      <c r="M32" s="110"/>
-      <c r="N32" s="110"/>
-      <c r="O32" s="110"/>
-      <c r="P32" s="110"/>
-      <c r="Q32" s="110"/>
-      <c r="R32" s="110"/>
-      <c r="S32" s="110"/>
-      <c r="T32" s="110"/>
-      <c r="U32" s="110"/>
-      <c r="V32" s="107"/>
-      <c r="W32" s="106"/>
-      <c r="X32" s="105"/>
-      <c r="Y32" s="107"/>
-      <c r="Z32" s="106"/>
-      <c r="AA32" s="105"/>
-      <c r="AB32" s="107"/>
-      <c r="AC32" s="106"/>
-      <c r="AD32" s="105"/>
-      <c r="AE32" s="107"/>
-      <c r="AF32" s="110"/>
-      <c r="AG32" s="110"/>
-      <c r="AH32" s="110"/>
-      <c r="AI32" s="110"/>
-      <c r="AJ32" s="110"/>
-      <c r="AK32" s="110"/>
-      <c r="AL32" s="110"/>
-      <c r="AM32" s="110"/>
-      <c r="AN32" s="110"/>
-      <c r="AO32" s="110"/>
-    </row>
-    <row r="33" spans="2:41" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="60"/>
-      <c r="C33" s="61"/>
-      <c r="D33" s="60"/>
-      <c r="E33" s="63"/>
-      <c r="F33" s="61"/>
-      <c r="G33" s="60"/>
-      <c r="H33" s="63"/>
-      <c r="I33" s="61"/>
-      <c r="J33" s="60"/>
-      <c r="K33" s="63"/>
-      <c r="L33" s="111"/>
-      <c r="M33" s="111"/>
-      <c r="N33" s="111"/>
-      <c r="O33" s="111"/>
-      <c r="P33" s="111"/>
-      <c r="Q33" s="111"/>
-      <c r="R33" s="111"/>
-      <c r="S33" s="111"/>
-      <c r="T33" s="111"/>
-      <c r="U33" s="111"/>
-      <c r="V33" s="63"/>
-      <c r="W33" s="61"/>
-      <c r="X33" s="60"/>
-      <c r="Y33" s="63"/>
-      <c r="Z33" s="61"/>
-      <c r="AA33" s="60"/>
-      <c r="AB33" s="63"/>
-      <c r="AC33" s="61"/>
-      <c r="AD33" s="60"/>
-      <c r="AE33" s="63"/>
-      <c r="AF33" s="112"/>
-      <c r="AG33" s="112"/>
-      <c r="AH33" s="112"/>
-      <c r="AI33" s="112"/>
-      <c r="AJ33" s="112"/>
-      <c r="AK33" s="112"/>
-      <c r="AL33" s="112"/>
-      <c r="AM33" s="112"/>
-      <c r="AN33" s="112"/>
-      <c r="AO33" s="112"/>
-    </row>
-    <row r="34" spans="2:41" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="67" t="s">
+    <row r="31" spans="1:40" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="69"/>
+      <c r="B31" s="70"/>
+      <c r="C31" s="69"/>
+      <c r="D31" s="74"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="69"/>
+      <c r="G31" s="74"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="69"/>
+      <c r="J31" s="74"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
+      <c r="O31" s="13"/>
+      <c r="P31" s="13"/>
+      <c r="Q31" s="13"/>
+      <c r="R31" s="13"/>
+      <c r="S31" s="13"/>
+      <c r="T31" s="13"/>
+      <c r="U31" s="74"/>
+      <c r="V31" s="70"/>
+      <c r="W31" s="69"/>
+      <c r="X31" s="74"/>
+      <c r="Y31" s="70"/>
+      <c r="Z31" s="69"/>
+      <c r="AA31" s="74"/>
+      <c r="AB31" s="70"/>
+      <c r="AC31" s="69"/>
+      <c r="AD31" s="74"/>
+      <c r="AE31" s="13"/>
+      <c r="AF31" s="13"/>
+      <c r="AG31" s="13"/>
+      <c r="AH31" s="13"/>
+      <c r="AI31" s="13"/>
+      <c r="AJ31" s="13"/>
+      <c r="AK31" s="13"/>
+      <c r="AL31" s="13"/>
+      <c r="AM31" s="13"/>
+      <c r="AN31" s="13"/>
+    </row>
+    <row r="32" spans="1:40" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="71"/>
+      <c r="B32" s="72"/>
+      <c r="C32" s="71"/>
+      <c r="D32" s="75"/>
+      <c r="E32" s="72"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="75"/>
+      <c r="H32" s="72"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="75"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="14"/>
+      <c r="M32" s="14"/>
+      <c r="N32" s="14"/>
+      <c r="O32" s="14"/>
+      <c r="P32" s="14"/>
+      <c r="Q32" s="14"/>
+      <c r="R32" s="14"/>
+      <c r="S32" s="14"/>
+      <c r="T32" s="14"/>
+      <c r="U32" s="75"/>
+      <c r="V32" s="72"/>
+      <c r="W32" s="71"/>
+      <c r="X32" s="75"/>
+      <c r="Y32" s="72"/>
+      <c r="Z32" s="71"/>
+      <c r="AA32" s="75"/>
+      <c r="AB32" s="72"/>
+      <c r="AC32" s="71"/>
+      <c r="AD32" s="75"/>
+      <c r="AE32" s="15"/>
+      <c r="AF32" s="15"/>
+      <c r="AG32" s="15"/>
+      <c r="AH32" s="15"/>
+      <c r="AI32" s="15"/>
+      <c r="AJ32" s="15"/>
+      <c r="AK32" s="15"/>
+      <c r="AL32" s="15"/>
+      <c r="AM32" s="15"/>
+      <c r="AN32" s="15"/>
+    </row>
+    <row r="33" spans="1:40" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="76" t="s">
         <v>62</v>
       </c>
-      <c r="C34" s="68"/>
-      <c r="D34" s="68"/>
-      <c r="E34" s="68"/>
-      <c r="F34" s="68"/>
-      <c r="G34" s="68"/>
-      <c r="H34" s="68"/>
-      <c r="I34" s="68"/>
-      <c r="J34" s="68"/>
-      <c r="K34" s="68"/>
-      <c r="L34" s="111"/>
-      <c r="M34" s="111"/>
-      <c r="N34" s="111"/>
-      <c r="O34" s="111"/>
-      <c r="P34" s="111"/>
-      <c r="Q34" s="111"/>
-      <c r="R34" s="111"/>
-      <c r="S34" s="111"/>
-      <c r="T34" s="111"/>
-      <c r="U34" s="111"/>
-      <c r="V34" s="68" t="s">
+      <c r="B33" s="77"/>
+      <c r="C33" s="77"/>
+      <c r="D33" s="77"/>
+      <c r="E33" s="77"/>
+      <c r="F33" s="77"/>
+      <c r="G33" s="77"/>
+      <c r="H33" s="77"/>
+      <c r="I33" s="77"/>
+      <c r="J33" s="77"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="14"/>
+      <c r="N33" s="14"/>
+      <c r="O33" s="14"/>
+      <c r="P33" s="14"/>
+      <c r="Q33" s="14"/>
+      <c r="R33" s="14"/>
+      <c r="S33" s="14"/>
+      <c r="T33" s="14"/>
+      <c r="U33" s="77" t="s">
         <v>63</v>
       </c>
-      <c r="W34" s="68"/>
-      <c r="X34" s="68"/>
-      <c r="Y34" s="68"/>
-      <c r="Z34" s="68"/>
-      <c r="AA34" s="68"/>
-      <c r="AB34" s="68"/>
-      <c r="AC34" s="68"/>
-      <c r="AD34" s="68"/>
-      <c r="AE34" s="68"/>
-      <c r="AF34" s="112"/>
-      <c r="AG34" s="112"/>
-      <c r="AH34" s="112"/>
-      <c r="AI34" s="112"/>
-      <c r="AJ34" s="112"/>
-      <c r="AK34" s="112"/>
-      <c r="AL34" s="112"/>
-      <c r="AM34" s="112"/>
-      <c r="AN34" s="112"/>
-      <c r="AO34" s="112"/>
-    </row>
-    <row r="35" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="101" t="s">
+      <c r="V33" s="77"/>
+      <c r="W33" s="77"/>
+      <c r="X33" s="77"/>
+      <c r="Y33" s="77"/>
+      <c r="Z33" s="77"/>
+      <c r="AA33" s="77"/>
+      <c r="AB33" s="77"/>
+      <c r="AC33" s="77"/>
+      <c r="AD33" s="77"/>
+      <c r="AE33" s="15"/>
+      <c r="AF33" s="15"/>
+      <c r="AG33" s="15"/>
+      <c r="AH33" s="15"/>
+      <c r="AI33" s="15"/>
+      <c r="AJ33" s="15"/>
+      <c r="AK33" s="15"/>
+      <c r="AL33" s="15"/>
+      <c r="AM33" s="15"/>
+      <c r="AN33" s="15"/>
+    </row>
+    <row r="34" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="78" t="s">
         <v>64</v>
       </c>
-      <c r="C35" s="101"/>
+      <c r="B34" s="78"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="10"/>
+      <c r="O34" s="10"/>
+      <c r="P34" s="11"/>
+      <c r="Q34" s="5"/>
+      <c r="R34" s="12"/>
+      <c r="S34" s="10"/>
+      <c r="T34" s="10"/>
+      <c r="U34" s="79" t="s">
+        <v>65</v>
+      </c>
+      <c r="V34" s="79"/>
+      <c r="W34" s="5"/>
+      <c r="X34" s="5"/>
+      <c r="Y34" s="5"/>
+      <c r="Z34" s="5"/>
+      <c r="AA34" s="5"/>
+      <c r="AB34" s="5"/>
+      <c r="AC34" s="8"/>
+      <c r="AD34" s="5"/>
+      <c r="AE34" s="9"/>
+      <c r="AF34" s="5"/>
+      <c r="AG34" s="5"/>
+      <c r="AH34" s="5"/>
+      <c r="AI34" s="5"/>
+      <c r="AJ34" s="5"/>
+      <c r="AK34" s="5"/>
+      <c r="AL34" s="5"/>
+      <c r="AM34" s="5"/>
+      <c r="AN34" s="5"/>
+    </row>
+    <row r="35" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="78" t="s">
+        <v>66</v>
+      </c>
+      <c r="B35" s="78"/>
+      <c r="C35" s="5"/>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
@@ -3902,29 +3948,29 @@
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
-      <c r="L35" s="104"/>
-      <c r="M35" s="104"/>
-      <c r="N35" s="104"/>
-      <c r="O35" s="104"/>
-      <c r="P35" s="104"/>
-      <c r="Q35" s="108"/>
-      <c r="R35" s="5"/>
-      <c r="S35" s="109"/>
-      <c r="T35" s="104"/>
-      <c r="U35" s="104"/>
-      <c r="V35" s="69" t="s">
-        <v>65</v>
-      </c>
-      <c r="W35" s="69"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="8"/>
+      <c r="Q35" s="5"/>
+      <c r="R35" s="9"/>
+      <c r="S35" s="5"/>
+      <c r="T35" s="5"/>
+      <c r="U35" s="79" t="s">
+        <v>67</v>
+      </c>
+      <c r="V35" s="79"/>
+      <c r="W35" s="5"/>
       <c r="X35" s="5"/>
       <c r="Y35" s="5"/>
       <c r="Z35" s="5"/>
       <c r="AA35" s="5"/>
       <c r="AB35" s="5"/>
-      <c r="AC35" s="5"/>
-      <c r="AD35" s="102"/>
-      <c r="AE35" s="5"/>
-      <c r="AF35" s="103"/>
+      <c r="AC35" s="8"/>
+      <c r="AD35" s="5"/>
+      <c r="AE35" s="9"/>
+      <c r="AF35" s="5"/>
       <c r="AG35" s="5"/>
       <c r="AH35" s="5"/>
       <c r="AI35" s="5"/>
@@ -3933,13 +3979,13 @@
       <c r="AL35" s="5"/>
       <c r="AM35" s="5"/>
       <c r="AN35" s="5"/>
-      <c r="AO35" s="5"/>
-    </row>
-    <row r="36" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="101" t="s">
-        <v>66</v>
-      </c>
-      <c r="C36" s="101"/>
+    </row>
+    <row r="36" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="78" t="s">
+        <v>68</v>
+      </c>
+      <c r="B36" s="78"/>
+      <c r="C36" s="5"/>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
@@ -3952,25 +3998,25 @@
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
       <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="102"/>
-      <c r="R36" s="5"/>
-      <c r="S36" s="103"/>
+      <c r="P36" s="8"/>
+      <c r="Q36" s="5"/>
+      <c r="R36" s="9"/>
+      <c r="S36" s="5"/>
       <c r="T36" s="5"/>
-      <c r="U36" s="5"/>
-      <c r="V36" s="69" t="s">
-        <v>67</v>
-      </c>
-      <c r="W36" s="69"/>
+      <c r="U36" s="79" t="s">
+        <v>68</v>
+      </c>
+      <c r="V36" s="79"/>
+      <c r="W36" s="5"/>
       <c r="X36" s="5"/>
       <c r="Y36" s="5"/>
       <c r="Z36" s="5"/>
       <c r="AA36" s="5"/>
       <c r="AB36" s="5"/>
-      <c r="AC36" s="5"/>
-      <c r="AD36" s="102"/>
-      <c r="AE36" s="5"/>
-      <c r="AF36" s="103"/>
+      <c r="AC36" s="8"/>
+      <c r="AD36" s="5"/>
+      <c r="AE36" s="9"/>
+      <c r="AF36" s="5"/>
       <c r="AG36" s="5"/>
       <c r="AH36" s="5"/>
       <c r="AI36" s="5"/>
@@ -3979,13 +4025,13 @@
       <c r="AL36" s="5"/>
       <c r="AM36" s="5"/>
       <c r="AN36" s="5"/>
-      <c r="AO36" s="5"/>
-    </row>
-    <row r="37" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="101" t="s">
-        <v>68</v>
-      </c>
-      <c r="C37" s="101"/>
+    </row>
+    <row r="37" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="78" t="s">
+        <v>69</v>
+      </c>
+      <c r="B37" s="78"/>
+      <c r="C37" s="5"/>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
@@ -3998,25 +4044,25 @@
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
       <c r="O37" s="5"/>
-      <c r="P37" s="5"/>
-      <c r="Q37" s="102"/>
-      <c r="R37" s="5"/>
-      <c r="S37" s="103"/>
+      <c r="P37" s="8"/>
+      <c r="Q37" s="5"/>
+      <c r="R37" s="9"/>
+      <c r="S37" s="5"/>
       <c r="T37" s="5"/>
-      <c r="U37" s="5"/>
-      <c r="V37" s="69" t="s">
-        <v>68</v>
-      </c>
-      <c r="W37" s="69"/>
+      <c r="U37" s="79" t="s">
+        <v>69</v>
+      </c>
+      <c r="V37" s="79"/>
+      <c r="W37" s="5"/>
       <c r="X37" s="5"/>
       <c r="Y37" s="5"/>
       <c r="Z37" s="5"/>
       <c r="AA37" s="5"/>
       <c r="AB37" s="5"/>
-      <c r="AC37" s="5"/>
-      <c r="AD37" s="102"/>
-      <c r="AE37" s="5"/>
-      <c r="AF37" s="103"/>
+      <c r="AC37" s="8"/>
+      <c r="AD37" s="5"/>
+      <c r="AE37" s="9"/>
+      <c r="AF37" s="5"/>
       <c r="AG37" s="5"/>
       <c r="AH37" s="5"/>
       <c r="AI37" s="5"/>
@@ -4025,13 +4071,13 @@
       <c r="AL37" s="5"/>
       <c r="AM37" s="5"/>
       <c r="AN37" s="5"/>
-      <c r="AO37" s="5"/>
-    </row>
-    <row r="38" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="101" t="s">
-        <v>69</v>
-      </c>
-      <c r="C38" s="101"/>
+    </row>
+    <row r="38" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="78" t="s">
+        <v>70</v>
+      </c>
+      <c r="B38" s="78"/>
+      <c r="C38" s="5"/>
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
@@ -4044,25 +4090,25 @@
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
       <c r="O38" s="5"/>
-      <c r="P38" s="5"/>
-      <c r="Q38" s="102"/>
-      <c r="R38" s="5"/>
-      <c r="S38" s="103"/>
+      <c r="P38" s="8"/>
+      <c r="Q38" s="5"/>
+      <c r="R38" s="9"/>
+      <c r="S38" s="5"/>
       <c r="T38" s="5"/>
-      <c r="U38" s="5"/>
-      <c r="V38" s="69" t="s">
-        <v>69</v>
-      </c>
-      <c r="W38" s="69"/>
+      <c r="U38" s="79" t="s">
+        <v>70</v>
+      </c>
+      <c r="V38" s="79"/>
+      <c r="W38" s="5"/>
       <c r="X38" s="5"/>
       <c r="Y38" s="5"/>
       <c r="Z38" s="5"/>
       <c r="AA38" s="5"/>
       <c r="AB38" s="5"/>
-      <c r="AC38" s="5"/>
-      <c r="AD38" s="102"/>
-      <c r="AE38" s="5"/>
-      <c r="AF38" s="103"/>
+      <c r="AC38" s="8"/>
+      <c r="AD38" s="5"/>
+      <c r="AE38" s="9"/>
+      <c r="AF38" s="5"/>
       <c r="AG38" s="5"/>
       <c r="AH38" s="5"/>
       <c r="AI38" s="5"/>
@@ -4071,13 +4117,13 @@
       <c r="AL38" s="5"/>
       <c r="AM38" s="5"/>
       <c r="AN38" s="5"/>
-      <c r="AO38" s="5"/>
-    </row>
-    <row r="39" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="101" t="s">
-        <v>70</v>
-      </c>
-      <c r="C39" s="101"/>
+    </row>
+    <row r="39" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="79" t="s">
+        <v>64</v>
+      </c>
+      <c r="B39" s="79"/>
+      <c r="C39" s="5"/>
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
@@ -4091,24 +4137,24 @@
       <c r="N39" s="5"/>
       <c r="O39" s="5"/>
       <c r="P39" s="5"/>
-      <c r="Q39" s="102"/>
+      <c r="Q39" s="10"/>
       <c r="R39" s="5"/>
-      <c r="S39" s="103"/>
+      <c r="S39" s="5"/>
       <c r="T39" s="5"/>
-      <c r="U39" s="5"/>
-      <c r="V39" s="69" t="s">
-        <v>70</v>
-      </c>
-      <c r="W39" s="69"/>
+      <c r="U39" s="79" t="s">
+        <v>65</v>
+      </c>
+      <c r="V39" s="79"/>
+      <c r="W39" s="5"/>
       <c r="X39" s="5"/>
       <c r="Y39" s="5"/>
       <c r="Z39" s="5"/>
       <c r="AA39" s="5"/>
       <c r="AB39" s="5"/>
       <c r="AC39" s="5"/>
-      <c r="AD39" s="102"/>
+      <c r="AD39" s="10"/>
       <c r="AE39" s="5"/>
-      <c r="AF39" s="103"/>
+      <c r="AF39" s="5"/>
       <c r="AG39" s="5"/>
       <c r="AH39" s="5"/>
       <c r="AI39" s="5"/>
@@ -4117,13 +4163,13 @@
       <c r="AL39" s="5"/>
       <c r="AM39" s="5"/>
       <c r="AN39" s="5"/>
-      <c r="AO39" s="5"/>
-    </row>
-    <row r="40" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="69" t="s">
-        <v>64</v>
-      </c>
-      <c r="C40" s="69"/>
+    </row>
+    <row r="40" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="79" t="s">
+        <v>66</v>
+      </c>
+      <c r="B40" s="79"/>
+      <c r="C40" s="5"/>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
@@ -4138,14 +4184,14 @@
       <c r="O40" s="5"/>
       <c r="P40" s="5"/>
       <c r="Q40" s="5"/>
-      <c r="R40" s="104"/>
+      <c r="R40" s="5"/>
       <c r="S40" s="5"/>
       <c r="T40" s="5"/>
-      <c r="U40" s="5"/>
-      <c r="V40" s="69" t="s">
-        <v>65</v>
-      </c>
-      <c r="W40" s="69"/>
+      <c r="U40" s="79" t="s">
+        <v>67</v>
+      </c>
+      <c r="V40" s="79"/>
+      <c r="W40" s="5"/>
       <c r="X40" s="5"/>
       <c r="Y40" s="5"/>
       <c r="Z40" s="5"/>
@@ -4153,7 +4199,7 @@
       <c r="AB40" s="5"/>
       <c r="AC40" s="5"/>
       <c r="AD40" s="5"/>
-      <c r="AE40" s="104"/>
+      <c r="AE40" s="5"/>
       <c r="AF40" s="5"/>
       <c r="AG40" s="5"/>
       <c r="AH40" s="5"/>
@@ -4163,13 +4209,13 @@
       <c r="AL40" s="5"/>
       <c r="AM40" s="5"/>
       <c r="AN40" s="5"/>
-      <c r="AO40" s="5"/>
-    </row>
-    <row r="41" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="69" t="s">
-        <v>66</v>
-      </c>
-      <c r="C41" s="69"/>
+    </row>
+    <row r="41" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="79" t="s">
+        <v>68</v>
+      </c>
+      <c r="B41" s="79"/>
+      <c r="C41" s="5"/>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
@@ -4187,11 +4233,11 @@
       <c r="R41" s="5"/>
       <c r="S41" s="5"/>
       <c r="T41" s="5"/>
-      <c r="U41" s="5"/>
-      <c r="V41" s="69" t="s">
-        <v>67</v>
-      </c>
-      <c r="W41" s="69"/>
+      <c r="U41" s="79" t="s">
+        <v>68</v>
+      </c>
+      <c r="V41" s="79"/>
+      <c r="W41" s="5"/>
       <c r="X41" s="5"/>
       <c r="Y41" s="5"/>
       <c r="Z41" s="5"/>
@@ -4209,13 +4255,13 @@
       <c r="AL41" s="5"/>
       <c r="AM41" s="5"/>
       <c r="AN41" s="5"/>
-      <c r="AO41" s="5"/>
-    </row>
-    <row r="42" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="69" t="s">
-        <v>68</v>
-      </c>
-      <c r="C42" s="69"/>
+    </row>
+    <row r="42" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="79" t="s">
+        <v>69</v>
+      </c>
+      <c r="B42" s="79"/>
+      <c r="C42" s="5"/>
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
@@ -4233,11 +4279,11 @@
       <c r="R42" s="5"/>
       <c r="S42" s="5"/>
       <c r="T42" s="5"/>
-      <c r="U42" s="5"/>
-      <c r="V42" s="69" t="s">
-        <v>68</v>
-      </c>
-      <c r="W42" s="69"/>
+      <c r="U42" s="79" t="s">
+        <v>69</v>
+      </c>
+      <c r="V42" s="79"/>
+      <c r="W42" s="5"/>
       <c r="X42" s="5"/>
       <c r="Y42" s="5"/>
       <c r="Z42" s="5"/>
@@ -4255,13 +4301,13 @@
       <c r="AL42" s="5"/>
       <c r="AM42" s="5"/>
       <c r="AN42" s="5"/>
-      <c r="AO42" s="5"/>
-    </row>
-    <row r="43" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="69" t="s">
-        <v>69</v>
-      </c>
-      <c r="C43" s="69"/>
+    </row>
+    <row r="43" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="79" t="s">
+        <v>70</v>
+      </c>
+      <c r="B43" s="79"/>
+      <c r="C43" s="5"/>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
@@ -4279,11 +4325,11 @@
       <c r="R43" s="5"/>
       <c r="S43" s="5"/>
       <c r="T43" s="5"/>
-      <c r="U43" s="5"/>
-      <c r="V43" s="69" t="s">
-        <v>69</v>
-      </c>
-      <c r="W43" s="69"/>
+      <c r="U43" s="79" t="s">
+        <v>70</v>
+      </c>
+      <c r="V43" s="79"/>
+      <c r="W43" s="5"/>
       <c r="X43" s="5"/>
       <c r="Y43" s="5"/>
       <c r="Z43" s="5"/>
@@ -4301,416 +4347,369 @@
       <c r="AL43" s="5"/>
       <c r="AM43" s="5"/>
       <c r="AN43" s="5"/>
-      <c r="AO43" s="5"/>
-    </row>
-    <row r="44" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="69" t="s">
-        <v>70</v>
-      </c>
-      <c r="C44" s="69"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
-      <c r="I44" s="5"/>
-      <c r="J44" s="5"/>
-      <c r="K44" s="5"/>
-      <c r="L44" s="5"/>
-      <c r="M44" s="5"/>
-      <c r="N44" s="5"/>
-      <c r="O44" s="5"/>
-      <c r="P44" s="5"/>
-      <c r="Q44" s="5"/>
-      <c r="R44" s="5"/>
-      <c r="S44" s="5"/>
-      <c r="T44" s="5"/>
-      <c r="U44" s="5"/>
-      <c r="V44" s="69" t="s">
-        <v>70</v>
-      </c>
-      <c r="W44" s="69"/>
-      <c r="X44" s="5"/>
-      <c r="Y44" s="5"/>
-      <c r="Z44" s="5"/>
-      <c r="AA44" s="5"/>
-      <c r="AB44" s="5"/>
-      <c r="AC44" s="5"/>
-      <c r="AD44" s="5"/>
-      <c r="AE44" s="5"/>
-      <c r="AF44" s="5"/>
-      <c r="AG44" s="5"/>
-      <c r="AH44" s="5"/>
-      <c r="AI44" s="5"/>
-      <c r="AJ44" s="5"/>
-      <c r="AK44" s="5"/>
-      <c r="AL44" s="5"/>
-      <c r="AM44" s="5"/>
-      <c r="AN44" s="5"/>
-      <c r="AO44" s="5"/>
-    </row>
-    <row r="45" spans="2:41" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="60" t="s">
+    </row>
+    <row r="44" spans="1:40" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="71" t="s">
         <v>71</v>
       </c>
+      <c r="B44" s="72"/>
+      <c r="C44" s="80" t="s">
+        <v>43</v>
+      </c>
+      <c r="D44" s="81"/>
+      <c r="E44" s="80" t="s">
+        <v>44</v>
+      </c>
+      <c r="F44" s="81"/>
+      <c r="G44" s="80" t="s">
+        <v>45</v>
+      </c>
+      <c r="H44" s="81"/>
+      <c r="I44" s="80" t="s">
+        <v>46</v>
+      </c>
+      <c r="J44" s="81"/>
+      <c r="K44" s="82" t="s">
+        <v>72</v>
+      </c>
+      <c r="L44" s="83"/>
+      <c r="M44" s="84" t="s">
+        <v>81</v>
+      </c>
+      <c r="N44" s="85"/>
+      <c r="O44" s="85"/>
+      <c r="P44" s="85"/>
+      <c r="Q44" s="85"/>
+      <c r="R44" s="85"/>
+      <c r="S44" s="85"/>
+      <c r="T44" s="86"/>
+      <c r="U44" s="87" t="s">
+        <v>83</v>
+      </c>
+      <c r="V44" s="88"/>
+      <c r="W44" s="88"/>
+      <c r="X44" s="88"/>
+      <c r="Y44" s="88"/>
+      <c r="Z44" s="89"/>
+      <c r="AA44" s="87" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB44" s="105"/>
+      <c r="AC44" s="105"/>
+      <c r="AD44" s="105"/>
+      <c r="AE44" s="105"/>
+      <c r="AF44" s="105"/>
+      <c r="AG44" s="106"/>
+      <c r="AH44" s="87" t="s">
+        <v>85</v>
+      </c>
+      <c r="AI44" s="105"/>
+      <c r="AJ44" s="105"/>
+      <c r="AK44" s="105"/>
+      <c r="AL44" s="105"/>
+      <c r="AM44" s="105"/>
+      <c r="AN44" s="106"/>
+    </row>
+    <row r="45" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="103" t="s">
+        <v>73</v>
+      </c>
+      <c r="B45" s="104"/>
       <c r="C45" s="61"/>
-      <c r="D45" s="70" t="s">
-        <v>43</v>
-      </c>
-      <c r="E45" s="71"/>
-      <c r="F45" s="70" t="s">
-        <v>44</v>
-      </c>
-      <c r="G45" s="71"/>
-      <c r="H45" s="70" t="s">
-        <v>45</v>
-      </c>
-      <c r="I45" s="71"/>
-      <c r="J45" s="70" t="s">
-        <v>46</v>
-      </c>
-      <c r="K45" s="71"/>
-      <c r="L45" s="72" t="s">
-        <v>72</v>
-      </c>
-      <c r="M45" s="73"/>
-      <c r="N45" s="74" t="s">
-        <v>81</v>
-      </c>
-      <c r="O45" s="75"/>
-      <c r="P45" s="75"/>
-      <c r="Q45" s="75"/>
-      <c r="R45" s="75"/>
-      <c r="S45" s="75"/>
-      <c r="T45" s="75"/>
-      <c r="U45" s="76"/>
-      <c r="V45" s="77" t="s">
-        <v>83</v>
-      </c>
-      <c r="W45" s="78"/>
-      <c r="X45" s="78"/>
-      <c r="Y45" s="78"/>
-      <c r="Z45" s="78"/>
-      <c r="AA45" s="79"/>
-      <c r="AB45" s="77" t="s">
-        <v>84</v>
-      </c>
-      <c r="AC45" s="93"/>
-      <c r="AD45" s="93"/>
-      <c r="AE45" s="93"/>
-      <c r="AF45" s="93"/>
-      <c r="AG45" s="93"/>
-      <c r="AH45" s="94"/>
-      <c r="AI45" s="77" t="s">
-        <v>85</v>
-      </c>
-      <c r="AJ45" s="93"/>
-      <c r="AK45" s="93"/>
-      <c r="AL45" s="93"/>
-      <c r="AM45" s="93"/>
-      <c r="AN45" s="93"/>
-      <c r="AO45" s="94"/>
-    </row>
-    <row r="46" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="39" t="s">
-        <v>73</v>
-      </c>
-      <c r="C46" s="40"/>
-      <c r="D46" s="55"/>
-      <c r="E46" s="57"/>
-      <c r="F46" s="55"/>
-      <c r="G46" s="57"/>
-      <c r="H46" s="55"/>
-      <c r="I46" s="57"/>
-      <c r="J46" s="55"/>
-      <c r="K46" s="57"/>
-      <c r="L46" s="55"/>
-      <c r="M46" s="57"/>
-      <c r="N46" s="55"/>
-      <c r="O46" s="56"/>
-      <c r="P46" s="56"/>
-      <c r="Q46" s="56"/>
-      <c r="R46" s="56"/>
-      <c r="S46" s="56"/>
-      <c r="T46" s="56"/>
-      <c r="U46" s="57"/>
-      <c r="V46" s="80"/>
-      <c r="W46" s="81"/>
-      <c r="X46" s="81"/>
-      <c r="Y46" s="81"/>
-      <c r="Z46" s="81"/>
-      <c r="AA46" s="82"/>
-      <c r="AB46" s="31"/>
-      <c r="AC46" s="32"/>
-      <c r="AD46" s="32"/>
-      <c r="AE46" s="32"/>
-      <c r="AF46" s="32"/>
-      <c r="AG46" s="32"/>
-      <c r="AH46" s="33"/>
-      <c r="AI46" s="31"/>
-      <c r="AJ46" s="32"/>
-      <c r="AK46" s="32"/>
-      <c r="AL46" s="32"/>
-      <c r="AM46" s="32"/>
-      <c r="AN46" s="32"/>
-      <c r="AO46" s="33"/>
-    </row>
-    <row r="47" spans="2:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="39" t="s">
+      <c r="D45" s="63"/>
+      <c r="E45" s="61"/>
+      <c r="F45" s="63"/>
+      <c r="G45" s="61"/>
+      <c r="H45" s="63"/>
+      <c r="I45" s="61"/>
+      <c r="J45" s="63"/>
+      <c r="K45" s="61"/>
+      <c r="L45" s="63"/>
+      <c r="M45" s="61"/>
+      <c r="N45" s="62"/>
+      <c r="O45" s="62"/>
+      <c r="P45" s="62"/>
+      <c r="Q45" s="62"/>
+      <c r="R45" s="62"/>
+      <c r="S45" s="62"/>
+      <c r="T45" s="63"/>
+      <c r="U45" s="90"/>
+      <c r="V45" s="91"/>
+      <c r="W45" s="91"/>
+      <c r="X45" s="91"/>
+      <c r="Y45" s="91"/>
+      <c r="Z45" s="92"/>
+      <c r="AA45" s="58"/>
+      <c r="AB45" s="59"/>
+      <c r="AC45" s="59"/>
+      <c r="AD45" s="59"/>
+      <c r="AE45" s="59"/>
+      <c r="AF45" s="59"/>
+      <c r="AG45" s="60"/>
+      <c r="AH45" s="58"/>
+      <c r="AI45" s="59"/>
+      <c r="AJ45" s="59"/>
+      <c r="AK45" s="59"/>
+      <c r="AL45" s="59"/>
+      <c r="AM45" s="59"/>
+      <c r="AN45" s="60"/>
+    </row>
+    <row r="46" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="103" t="s">
         <v>74</v>
       </c>
-      <c r="C47" s="40"/>
-      <c r="D47" s="55"/>
-      <c r="E47" s="57"/>
-      <c r="F47" s="55"/>
-      <c r="G47" s="57"/>
-      <c r="H47" s="55"/>
-      <c r="I47" s="57"/>
-      <c r="J47" s="55"/>
-      <c r="K47" s="57"/>
-      <c r="L47" s="55"/>
-      <c r="M47" s="57"/>
-      <c r="N47" s="55"/>
-      <c r="O47" s="56"/>
-      <c r="P47" s="56"/>
-      <c r="Q47" s="56"/>
-      <c r="R47" s="56"/>
-      <c r="S47" s="56"/>
-      <c r="T47" s="56"/>
-      <c r="U47" s="57"/>
-      <c r="V47" s="83" t="s">
+      <c r="B46" s="104"/>
+      <c r="C46" s="61"/>
+      <c r="D46" s="63"/>
+      <c r="E46" s="61"/>
+      <c r="F46" s="63"/>
+      <c r="G46" s="61"/>
+      <c r="H46" s="63"/>
+      <c r="I46" s="61"/>
+      <c r="J46" s="63"/>
+      <c r="K46" s="61"/>
+      <c r="L46" s="63"/>
+      <c r="M46" s="61"/>
+      <c r="N46" s="62"/>
+      <c r="O46" s="62"/>
+      <c r="P46" s="62"/>
+      <c r="Q46" s="62"/>
+      <c r="R46" s="62"/>
+      <c r="S46" s="62"/>
+      <c r="T46" s="63"/>
+      <c r="U46" s="93" t="s">
         <v>75</v>
       </c>
-      <c r="W47" s="84"/>
-      <c r="X47" s="84"/>
-      <c r="Y47" s="84"/>
-      <c r="Z47" s="84"/>
-      <c r="AA47" s="85"/>
-      <c r="AB47" s="83" t="s">
+      <c r="V46" s="94"/>
+      <c r="W46" s="94"/>
+      <c r="X46" s="94"/>
+      <c r="Y46" s="94"/>
+      <c r="Z46" s="95"/>
+      <c r="AA46" s="93" t="s">
         <v>76</v>
       </c>
-      <c r="AC47" s="84"/>
-      <c r="AD47" s="84"/>
-      <c r="AE47" s="84"/>
-      <c r="AF47" s="84"/>
-      <c r="AG47" s="84"/>
-      <c r="AH47" s="85"/>
-      <c r="AI47" s="83" t="s">
+      <c r="AB46" s="94"/>
+      <c r="AC46" s="94"/>
+      <c r="AD46" s="94"/>
+      <c r="AE46" s="94"/>
+      <c r="AF46" s="94"/>
+      <c r="AG46" s="95"/>
+      <c r="AH46" s="93" t="s">
         <v>77</v>
       </c>
-      <c r="AJ47" s="84"/>
-      <c r="AK47" s="84"/>
-      <c r="AL47" s="84"/>
-      <c r="AM47" s="84"/>
-      <c r="AN47" s="84"/>
-      <c r="AO47" s="85"/>
-    </row>
-    <row r="48" spans="2:41" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="8" t="s">
+      <c r="AI46" s="94"/>
+      <c r="AJ46" s="94"/>
+      <c r="AK46" s="94"/>
+      <c r="AL46" s="94"/>
+      <c r="AM46" s="94"/>
+      <c r="AN46" s="95"/>
+    </row>
+    <row r="47" spans="1:40" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9"/>
-      <c r="H48" s="9"/>
-      <c r="I48" s="9"/>
-      <c r="J48" s="9"/>
-      <c r="K48" s="9"/>
-      <c r="L48" s="9"/>
-      <c r="M48" s="9"/>
-      <c r="N48" s="9"/>
-      <c r="O48" s="9"/>
-      <c r="P48" s="9"/>
-      <c r="Q48" s="9"/>
-      <c r="R48" s="9"/>
-      <c r="S48" s="9"/>
-      <c r="T48" s="9"/>
-      <c r="U48" s="10"/>
-      <c r="V48" s="80"/>
-      <c r="W48" s="81"/>
-      <c r="X48" s="81"/>
-      <c r="Y48" s="81"/>
-      <c r="Z48" s="81"/>
-      <c r="AA48" s="82"/>
-      <c r="AB48" s="80"/>
-      <c r="AC48" s="81"/>
-      <c r="AD48" s="81"/>
-      <c r="AE48" s="81"/>
-      <c r="AF48" s="81"/>
-      <c r="AG48" s="81"/>
-      <c r="AH48" s="82"/>
-      <c r="AI48" s="80"/>
-      <c r="AJ48" s="81"/>
-      <c r="AK48" s="81"/>
-      <c r="AL48" s="81"/>
-      <c r="AM48" s="81"/>
-      <c r="AN48" s="81"/>
-      <c r="AO48" s="82"/>
+      <c r="B47" s="20"/>
+      <c r="C47" s="20"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="20"/>
+      <c r="H47" s="20"/>
+      <c r="I47" s="20"/>
+      <c r="J47" s="20"/>
+      <c r="K47" s="20"/>
+      <c r="L47" s="20"/>
+      <c r="M47" s="20"/>
+      <c r="N47" s="20"/>
+      <c r="O47" s="20"/>
+      <c r="P47" s="20"/>
+      <c r="Q47" s="20"/>
+      <c r="R47" s="20"/>
+      <c r="S47" s="20"/>
+      <c r="T47" s="21"/>
+      <c r="U47" s="90"/>
+      <c r="V47" s="91"/>
+      <c r="W47" s="91"/>
+      <c r="X47" s="91"/>
+      <c r="Y47" s="91"/>
+      <c r="Z47" s="92"/>
+      <c r="AA47" s="90"/>
+      <c r="AB47" s="91"/>
+      <c r="AC47" s="91"/>
+      <c r="AD47" s="91"/>
+      <c r="AE47" s="91"/>
+      <c r="AF47" s="91"/>
+      <c r="AG47" s="92"/>
+      <c r="AH47" s="90"/>
+      <c r="AI47" s="91"/>
+      <c r="AJ47" s="91"/>
+      <c r="AK47" s="91"/>
+      <c r="AL47" s="91"/>
+      <c r="AM47" s="91"/>
+      <c r="AN47" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="160">
-    <mergeCell ref="AI47:AO48"/>
-    <mergeCell ref="B48:U48"/>
-    <mergeCell ref="J2:AA3"/>
-    <mergeCell ref="AB2:AG3"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="J47:K47"/>
-    <mergeCell ref="L47:M47"/>
-    <mergeCell ref="N47:U47"/>
-    <mergeCell ref="V47:AA48"/>
-    <mergeCell ref="AB47:AH48"/>
-    <mergeCell ref="AB45:AH46"/>
-    <mergeCell ref="AI45:AO46"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="J46:K46"/>
-    <mergeCell ref="L46:M46"/>
-    <mergeCell ref="N46:U46"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="V43:W43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="V44:W44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="L45:M45"/>
-    <mergeCell ref="N45:U45"/>
-    <mergeCell ref="V45:AA46"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="V38:W38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="V39:W39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="V40:W40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="V41:W41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="V42:W42"/>
-    <mergeCell ref="B34:K34"/>
-    <mergeCell ref="V34:AE34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="V35:W35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="V36:W36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="V37:W37"/>
-    <mergeCell ref="AA31:AC33"/>
-    <mergeCell ref="AD31:AE33"/>
-    <mergeCell ref="AF31:AH31"/>
-    <mergeCell ref="AI31:AK31"/>
-    <mergeCell ref="AL31:AN31"/>
-    <mergeCell ref="B31:C33"/>
-    <mergeCell ref="D31:F33"/>
-    <mergeCell ref="G31:I33"/>
-    <mergeCell ref="J31:K33"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="R31:T31"/>
-    <mergeCell ref="V31:W33"/>
-    <mergeCell ref="X31:Z33"/>
-    <mergeCell ref="B27:I27"/>
-    <mergeCell ref="K27:U27"/>
-    <mergeCell ref="V27:AC27"/>
-    <mergeCell ref="AE27:AO27"/>
-    <mergeCell ref="B28:I28"/>
-    <mergeCell ref="V28:AC28"/>
-    <mergeCell ref="B29:I29"/>
-    <mergeCell ref="V29:AC29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="L30:U30"/>
-    <mergeCell ref="V30:W30"/>
-    <mergeCell ref="X30:Z30"/>
-    <mergeCell ref="AA30:AC30"/>
-    <mergeCell ref="AD30:AE30"/>
-    <mergeCell ref="AF30:AO30"/>
-    <mergeCell ref="C22:I22"/>
-    <mergeCell ref="W22:AC22"/>
-    <mergeCell ref="C23:I23"/>
-    <mergeCell ref="W23:AC23"/>
-    <mergeCell ref="C24:I24"/>
-    <mergeCell ref="W24:AC24"/>
-    <mergeCell ref="C25:I25"/>
-    <mergeCell ref="W25:AC25"/>
-    <mergeCell ref="C26:I26"/>
-    <mergeCell ref="W26:AC26"/>
-    <mergeCell ref="C17:I17"/>
-    <mergeCell ref="W17:AC17"/>
-    <mergeCell ref="C18:I18"/>
-    <mergeCell ref="W18:AC18"/>
-    <mergeCell ref="C19:I19"/>
-    <mergeCell ref="W19:AC19"/>
-    <mergeCell ref="C20:I20"/>
-    <mergeCell ref="W20:AC20"/>
-    <mergeCell ref="C21:I21"/>
-    <mergeCell ref="W21:AC21"/>
-    <mergeCell ref="C12:I12"/>
-    <mergeCell ref="W12:AC12"/>
-    <mergeCell ref="C13:I13"/>
-    <mergeCell ref="W13:AC13"/>
-    <mergeCell ref="C14:I14"/>
-    <mergeCell ref="W14:AC14"/>
-    <mergeCell ref="C15:I15"/>
-    <mergeCell ref="W15:AC15"/>
-    <mergeCell ref="C16:I16"/>
-    <mergeCell ref="W16:AC16"/>
-    <mergeCell ref="J9:U9"/>
-    <mergeCell ref="V9:AG9"/>
-    <mergeCell ref="AH9:AJ9"/>
-    <mergeCell ref="AL9:AN9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:I10"/>
-    <mergeCell ref="K10:Q10"/>
-    <mergeCell ref="R10:U10"/>
-    <mergeCell ref="V10:V11"/>
-    <mergeCell ref="W10:AC10"/>
-    <mergeCell ref="AE10:AK10"/>
-    <mergeCell ref="AL10:AO10"/>
-    <mergeCell ref="C11:I11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="W11:AC11"/>
-    <mergeCell ref="AE11:AF11"/>
-    <mergeCell ref="AG11:AH11"/>
-    <mergeCell ref="AI11:AJ11"/>
-    <mergeCell ref="B2:I9"/>
-    <mergeCell ref="AH2:AO2"/>
-    <mergeCell ref="AH3:AO3"/>
-    <mergeCell ref="J4:AG5"/>
-    <mergeCell ref="AH4:AJ4"/>
-    <mergeCell ref="AL4:AN4"/>
-    <mergeCell ref="AH5:AJ5"/>
-    <mergeCell ref="AL5:AN5"/>
-    <mergeCell ref="J6:AG6"/>
-    <mergeCell ref="AH6:AJ6"/>
-    <mergeCell ref="AL6:AN6"/>
-    <mergeCell ref="J7:O7"/>
-    <mergeCell ref="P7:S7"/>
-    <mergeCell ref="T7:W7"/>
-    <mergeCell ref="X7:AA7"/>
-    <mergeCell ref="AB7:AE7"/>
-    <mergeCell ref="AF7:AG8"/>
-    <mergeCell ref="AH7:AJ7"/>
-    <mergeCell ref="AL7:AN7"/>
-    <mergeCell ref="J8:O8"/>
-    <mergeCell ref="P8:T8"/>
-    <mergeCell ref="U8:W8"/>
-    <mergeCell ref="X8:AA8"/>
-    <mergeCell ref="AB8:AE8"/>
-    <mergeCell ref="AH8:AJ8"/>
-    <mergeCell ref="AL8:AN8"/>
+    <mergeCell ref="AH46:AN47"/>
+    <mergeCell ref="A47:T47"/>
+    <mergeCell ref="I1:Z2"/>
+    <mergeCell ref="AA1:AF2"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="M46:T46"/>
+    <mergeCell ref="U46:Z47"/>
+    <mergeCell ref="AA46:AG47"/>
+    <mergeCell ref="AA44:AG45"/>
+    <mergeCell ref="AH44:AN45"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="K45:L45"/>
+    <mergeCell ref="M45:T45"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="U42:V42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="U43:V43"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="M44:T44"/>
+    <mergeCell ref="U44:Z45"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="U37:V37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="U38:V38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="U39:V39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="U40:V40"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="U41:V41"/>
+    <mergeCell ref="A33:J33"/>
+    <mergeCell ref="U33:AD33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="U34:V34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="U35:V35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="U36:V36"/>
+    <mergeCell ref="Z30:AB32"/>
+    <mergeCell ref="AC30:AD32"/>
+    <mergeCell ref="AE30:AG30"/>
+    <mergeCell ref="AH30:AJ30"/>
+    <mergeCell ref="AK30:AM30"/>
+    <mergeCell ref="A30:B32"/>
+    <mergeCell ref="C30:E32"/>
+    <mergeCell ref="F30:H32"/>
+    <mergeCell ref="I30:J32"/>
+    <mergeCell ref="K30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="Q30:S30"/>
+    <mergeCell ref="U30:V32"/>
+    <mergeCell ref="W30:Y32"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="J26:T26"/>
+    <mergeCell ref="U26:AB26"/>
+    <mergeCell ref="AD26:AN26"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="U27:AB27"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="U28:AB28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="K29:T29"/>
+    <mergeCell ref="U29:V29"/>
+    <mergeCell ref="W29:Y29"/>
+    <mergeCell ref="Z29:AB29"/>
+    <mergeCell ref="AC29:AD29"/>
+    <mergeCell ref="AE29:AN29"/>
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="V21:AB21"/>
+    <mergeCell ref="B22:H22"/>
+    <mergeCell ref="V22:AB22"/>
+    <mergeCell ref="B23:H23"/>
+    <mergeCell ref="V23:AB23"/>
+    <mergeCell ref="B24:H24"/>
+    <mergeCell ref="V24:AB24"/>
+    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="V25:AB25"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="V16:AB16"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="V17:AB17"/>
+    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="V18:AB18"/>
+    <mergeCell ref="B19:H19"/>
+    <mergeCell ref="V19:AB19"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="V20:AB20"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="V11:AB11"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="V12:AB12"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="V13:AB13"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="V14:AB14"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="V15:AB15"/>
+    <mergeCell ref="I8:T8"/>
+    <mergeCell ref="U8:AF8"/>
+    <mergeCell ref="AG8:AI8"/>
+    <mergeCell ref="AK8:AM8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:T9"/>
+    <mergeCell ref="U9:U10"/>
+    <mergeCell ref="V9:AB9"/>
+    <mergeCell ref="AD9:AJ9"/>
+    <mergeCell ref="AK9:AN9"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="V10:AB10"/>
+    <mergeCell ref="AD10:AE10"/>
+    <mergeCell ref="AF10:AG10"/>
+    <mergeCell ref="AH10:AI10"/>
+    <mergeCell ref="A1:H8"/>
+    <mergeCell ref="AG1:AN1"/>
+    <mergeCell ref="AG2:AN2"/>
+    <mergeCell ref="I3:AF4"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="AK3:AM3"/>
+    <mergeCell ref="AG4:AI4"/>
+    <mergeCell ref="AK4:AM4"/>
+    <mergeCell ref="I5:AF5"/>
+    <mergeCell ref="AG5:AI5"/>
+    <mergeCell ref="AK5:AM5"/>
+    <mergeCell ref="I6:N6"/>
+    <mergeCell ref="O6:R6"/>
+    <mergeCell ref="S6:V6"/>
+    <mergeCell ref="W6:Z6"/>
+    <mergeCell ref="AA6:AD6"/>
+    <mergeCell ref="AE6:AF7"/>
+    <mergeCell ref="AG6:AI6"/>
+    <mergeCell ref="AK6:AM6"/>
+    <mergeCell ref="I7:N7"/>
+    <mergeCell ref="O7:S7"/>
+    <mergeCell ref="T7:V7"/>
+    <mergeCell ref="W7:Z7"/>
+    <mergeCell ref="AA7:AD7"/>
+    <mergeCell ref="AG7:AI7"/>
+    <mergeCell ref="AK7:AM7"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="55" orientation="landscape" r:id="rId1"/>
@@ -4724,114 +4723,114 @@
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="3" spans="6:29" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F3" s="95" t="s">
+      <c r="F3" s="107" t="s">
         <v>0</v>
       </c>
-      <c r="G3" s="96"/>
-      <c r="H3" s="96"/>
-      <c r="I3" s="96"/>
-      <c r="J3" s="96"/>
-      <c r="K3" s="96"/>
-      <c r="L3" s="96"/>
-      <c r="M3" s="96"/>
-      <c r="N3" s="96"/>
-      <c r="O3" s="96"/>
-      <c r="P3" s="96"/>
-      <c r="Q3" s="96"/>
-      <c r="R3" s="96"/>
-      <c r="S3" s="96"/>
-      <c r="T3" s="96"/>
-      <c r="U3" s="96"/>
-      <c r="V3" s="96"/>
-      <c r="W3" s="96"/>
-      <c r="X3" s="96"/>
-      <c r="Y3" s="96"/>
-      <c r="Z3" s="96"/>
-      <c r="AA3" s="96"/>
-      <c r="AB3" s="96"/>
-      <c r="AC3" s="97"/>
+      <c r="G3" s="108"/>
+      <c r="H3" s="108"/>
+      <c r="I3" s="108"/>
+      <c r="J3" s="108"/>
+      <c r="K3" s="108"/>
+      <c r="L3" s="108"/>
+      <c r="M3" s="108"/>
+      <c r="N3" s="108"/>
+      <c r="O3" s="108"/>
+      <c r="P3" s="108"/>
+      <c r="Q3" s="108"/>
+      <c r="R3" s="108"/>
+      <c r="S3" s="108"/>
+      <c r="T3" s="108"/>
+      <c r="U3" s="108"/>
+      <c r="V3" s="108"/>
+      <c r="W3" s="108"/>
+      <c r="X3" s="108"/>
+      <c r="Y3" s="108"/>
+      <c r="Z3" s="108"/>
+      <c r="AA3" s="108"/>
+      <c r="AB3" s="108"/>
+      <c r="AC3" s="109"/>
     </row>
     <row r="4" spans="6:29" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F4" s="98"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="99"/>
-      <c r="K4" s="99"/>
-      <c r="L4" s="99"/>
-      <c r="M4" s="99"/>
-      <c r="N4" s="99"/>
-      <c r="O4" s="99"/>
-      <c r="P4" s="99"/>
-      <c r="Q4" s="99"/>
-      <c r="R4" s="99"/>
-      <c r="S4" s="99"/>
-      <c r="T4" s="99"/>
-      <c r="U4" s="99"/>
-      <c r="V4" s="99"/>
-      <c r="W4" s="99"/>
-      <c r="X4" s="99"/>
-      <c r="Y4" s="99"/>
-      <c r="Z4" s="99"/>
-      <c r="AA4" s="99"/>
-      <c r="AB4" s="99"/>
-      <c r="AC4" s="100"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="111"/>
+      <c r="L4" s="111"/>
+      <c r="M4" s="111"/>
+      <c r="N4" s="111"/>
+      <c r="O4" s="111"/>
+      <c r="P4" s="111"/>
+      <c r="Q4" s="111"/>
+      <c r="R4" s="111"/>
+      <c r="S4" s="111"/>
+      <c r="T4" s="111"/>
+      <c r="U4" s="111"/>
+      <c r="V4" s="111"/>
+      <c r="W4" s="111"/>
+      <c r="X4" s="111"/>
+      <c r="Y4" s="111"/>
+      <c r="Z4" s="111"/>
+      <c r="AA4" s="111"/>
+      <c r="AB4" s="111"/>
+      <c r="AC4" s="112"/>
     </row>
     <row r="7" spans="6:29" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F7" s="86" t="s">
+      <c r="F7" s="96" t="s">
         <v>79</v>
       </c>
-      <c r="G7" s="87"/>
-      <c r="H7" s="87"/>
-      <c r="I7" s="87"/>
-      <c r="J7" s="87"/>
-      <c r="K7" s="87"/>
-      <c r="L7" s="87"/>
-      <c r="M7" s="87"/>
-      <c r="N7" s="87"/>
-      <c r="O7" s="87"/>
-      <c r="P7" s="87"/>
-      <c r="Q7" s="87"/>
-      <c r="R7" s="87"/>
-      <c r="S7" s="87"/>
-      <c r="T7" s="87"/>
-      <c r="U7" s="87"/>
-      <c r="V7" s="87"/>
-      <c r="W7" s="87"/>
-      <c r="X7" s="90" t="s">
+      <c r="G7" s="97"/>
+      <c r="H7" s="97"/>
+      <c r="I7" s="97"/>
+      <c r="J7" s="97"/>
+      <c r="K7" s="97"/>
+      <c r="L7" s="97"/>
+      <c r="M7" s="97"/>
+      <c r="N7" s="97"/>
+      <c r="O7" s="97"/>
+      <c r="P7" s="97"/>
+      <c r="Q7" s="97"/>
+      <c r="R7" s="97"/>
+      <c r="S7" s="97"/>
+      <c r="T7" s="97"/>
+      <c r="U7" s="97"/>
+      <c r="V7" s="97"/>
+      <c r="W7" s="97"/>
+      <c r="X7" s="100" t="s">
         <v>82</v>
       </c>
-      <c r="Y7" s="91"/>
-      <c r="Z7" s="91"/>
-      <c r="AA7" s="91"/>
-      <c r="AB7" s="91"/>
-      <c r="AC7" s="15"/>
+      <c r="Y7" s="101"/>
+      <c r="Z7" s="101"/>
+      <c r="AA7" s="101"/>
+      <c r="AB7" s="101"/>
+      <c r="AC7" s="26"/>
     </row>
     <row r="8" spans="6:29" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F8" s="88"/>
-      <c r="G8" s="89"/>
-      <c r="H8" s="89"/>
-      <c r="I8" s="89"/>
-      <c r="J8" s="89"/>
-      <c r="K8" s="89"/>
-      <c r="L8" s="89"/>
-      <c r="M8" s="89"/>
-      <c r="N8" s="89"/>
-      <c r="O8" s="89"/>
-      <c r="P8" s="89"/>
-      <c r="Q8" s="89"/>
-      <c r="R8" s="89"/>
-      <c r="S8" s="89"/>
-      <c r="T8" s="89"/>
-      <c r="U8" s="89"/>
-      <c r="V8" s="89"/>
-      <c r="W8" s="89"/>
-      <c r="X8" s="92"/>
-      <c r="Y8" s="92"/>
-      <c r="Z8" s="92"/>
-      <c r="AA8" s="92"/>
-      <c r="AB8" s="92"/>
-      <c r="AC8" s="17"/>
+      <c r="F8" s="98"/>
+      <c r="G8" s="99"/>
+      <c r="H8" s="99"/>
+      <c r="I8" s="99"/>
+      <c r="J8" s="99"/>
+      <c r="K8" s="99"/>
+      <c r="L8" s="99"/>
+      <c r="M8" s="99"/>
+      <c r="N8" s="99"/>
+      <c r="O8" s="99"/>
+      <c r="P8" s="99"/>
+      <c r="Q8" s="99"/>
+      <c r="R8" s="99"/>
+      <c r="S8" s="99"/>
+      <c r="T8" s="99"/>
+      <c r="U8" s="99"/>
+      <c r="V8" s="99"/>
+      <c r="W8" s="99"/>
+      <c r="X8" s="102"/>
+      <c r="Y8" s="102"/>
+      <c r="Z8" s="102"/>
+      <c r="AA8" s="102"/>
+      <c r="AB8" s="102"/>
+      <c r="AC8" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/assets/files/base_scoresheet.xlsx
+++ b/assets/files/base_scoresheet.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Parth\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Parth\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1564985-7905-4E77-9DDD-AA3A75F73717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{321775A9-FCBC-4A1C-AF26-C4AE5AE7DF52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="93">
   <si>
     <r>
       <rPr>
@@ -785,25 +785,6 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">POINTS                TURNS
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7.5"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>SCORED BY</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="7.5"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
       <t>GRAND TOTAL</t>
     </r>
   </si>
@@ -959,6 +940,26 @@
       <t>KHO KHO FEDERATION OF INDIA
 MAHARASHTRA OLYMPIC ASSOCIATION</t>
     </r>
+  </si>
+  <si>
+    <t>POINTS
+SCORED BY</t>
+  </si>
+  <si>
+    <t>Inning 
+I</t>
+  </si>
+  <si>
+    <t>Inning 
+II</t>
+  </si>
+  <si>
+    <t>Inning 
+III</t>
+  </si>
+  <si>
+    <t>Inning 
+IV</t>
   </si>
 </sst>
 </file>
@@ -1427,15 +1428,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1577,7 +1569,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1646,12 +1638,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1675,6 +1661,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1695,146 +1696,6 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>346456</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>209549</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="349250" cy="212090"/>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="164" name="Group 164">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A4000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="773176" y="9216389"/>
-          <a:ext cx="349250" cy="212090"/>
-          <a:chOff x="0" y="0"/>
-          <a:chExt cx="349250" cy="212090"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="165" name="Shape 165">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A5000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="761" y="761"/>
-            <a:ext cx="347980" cy="210820"/>
-          </a:xfrm>
-          <a:custGeom>
-            <a:avLst/>
-            <a:gdLst/>
-            <a:ahLst/>
-            <a:cxnLst/>
-            <a:rect l="0" t="0" r="0" b="0"/>
-            <a:pathLst>
-              <a:path w="347980" h="210820">
-                <a:moveTo>
-                  <a:pt x="347472" y="210311"/>
-                </a:moveTo>
-                <a:lnTo>
-                  <a:pt x="347472" y="205740"/>
-                </a:lnTo>
-                <a:lnTo>
-                  <a:pt x="9144" y="0"/>
-                </a:lnTo>
-                <a:lnTo>
-                  <a:pt x="0" y="0"/>
-                </a:lnTo>
-                <a:lnTo>
-                  <a:pt x="0" y="4572"/>
-                </a:lnTo>
-                <a:lnTo>
-                  <a:pt x="338328" y="210311"/>
-                </a:lnTo>
-                <a:lnTo>
-                  <a:pt x="347472" y="210311"/>
-                </a:lnTo>
-                <a:close/>
-              </a:path>
-            </a:pathLst>
-          </a:custGeom>
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-        </xdr:spPr>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="166" name="Shape 166">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000A6000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="761" y="761"/>
-            <a:ext cx="347980" cy="210820"/>
-          </a:xfrm>
-          <a:custGeom>
-            <a:avLst/>
-            <a:gdLst/>
-            <a:ahLst/>
-            <a:cxnLst/>
-            <a:rect l="0" t="0" r="0" b="0"/>
-            <a:pathLst>
-              <a:path w="347980" h="210820">
-                <a:moveTo>
-                  <a:pt x="0" y="0"/>
-                </a:moveTo>
-                <a:lnTo>
-                  <a:pt x="9144" y="0"/>
-                </a:lnTo>
-                <a:lnTo>
-                  <a:pt x="347472" y="205740"/>
-                </a:lnTo>
-                <a:lnTo>
-                  <a:pt x="347472" y="210311"/>
-                </a:lnTo>
-                <a:lnTo>
-                  <a:pt x="338328" y="210311"/>
-                </a:lnTo>
-                <a:lnTo>
-                  <a:pt x="0" y="4572"/>
-                </a:lnTo>
-                <a:lnTo>
-                  <a:pt x="0" y="0"/>
-                </a:lnTo>
-                <a:close/>
-              </a:path>
-            </a:pathLst>
-          </a:custGeom>
-          <a:ln w="3175">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -2216,7 +2077,8 @@
     <col min="5" max="5" width="6.44140625" customWidth="1"/>
     <col min="6" max="7" width="6.21875" customWidth="1"/>
     <col min="8" max="8" width="6.44140625" customWidth="1"/>
-    <col min="9" max="10" width="6.21875" customWidth="1"/>
+    <col min="9" max="9" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.21875" customWidth="1"/>
     <col min="11" max="11" width="6.44140625" customWidth="1"/>
     <col min="12" max="13" width="6.21875" customWidth="1"/>
     <col min="14" max="14" width="6.44140625" customWidth="1"/>
@@ -2224,7 +2086,8 @@
     <col min="17" max="17" width="6.44140625" customWidth="1"/>
     <col min="18" max="18" width="6.21875" customWidth="1"/>
     <col min="19" max="19" width="6.44140625" customWidth="1"/>
-    <col min="20" max="21" width="6.21875" customWidth="1"/>
+    <col min="20" max="20" width="6.21875" customWidth="1"/>
+    <col min="21" max="21" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="12.6640625" customWidth="1"/>
     <col min="23" max="23" width="6.21875" customWidth="1"/>
     <col min="24" max="24" width="6.44140625" customWidth="1"/>
@@ -2243,134 +2106,134 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="93" t="s">
+        <v>78</v>
+      </c>
+      <c r="J1" s="94"/>
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
+      <c r="M1" s="94"/>
+      <c r="N1" s="94"/>
+      <c r="O1" s="94"/>
+      <c r="P1" s="94"/>
+      <c r="Q1" s="94"/>
+      <c r="R1" s="94"/>
+      <c r="S1" s="94"/>
+      <c r="T1" s="94"/>
+      <c r="U1" s="94"/>
+      <c r="V1" s="94"/>
+      <c r="W1" s="94"/>
+      <c r="X1" s="94"/>
+      <c r="Y1" s="94"/>
+      <c r="Z1" s="94"/>
+      <c r="AA1" s="97" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB1" s="98"/>
+      <c r="AC1" s="98"/>
+      <c r="AD1" s="98"/>
+      <c r="AE1" s="98"/>
+      <c r="AF1" s="26"/>
+      <c r="AG1" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="96" t="s">
-        <v>79</v>
-      </c>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="100" t="s">
-        <v>88</v>
-      </c>
-      <c r="AB1" s="101"/>
-      <c r="AC1" s="101"/>
-      <c r="AD1" s="101"/>
-      <c r="AE1" s="101"/>
-      <c r="AF1" s="26"/>
-      <c r="AG1" s="49" t="s">
-        <v>80</v>
-      </c>
-      <c r="AH1" s="50"/>
-      <c r="AI1" s="50"/>
-      <c r="AJ1" s="50"/>
-      <c r="AK1" s="50"/>
-      <c r="AL1" s="50"/>
-      <c r="AM1" s="50"/>
-      <c r="AN1" s="51"/>
+      <c r="AH1" s="47"/>
+      <c r="AI1" s="47"/>
+      <c r="AJ1" s="47"/>
+      <c r="AK1" s="47"/>
+      <c r="AL1" s="47"/>
+      <c r="AM1" s="47"/>
+      <c r="AN1" s="48"/>
     </row>
     <row r="2" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="43"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="99"/>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="99"/>
-      <c r="R2" s="99"/>
-      <c r="S2" s="99"/>
-      <c r="T2" s="99"/>
-      <c r="U2" s="99"/>
-      <c r="V2" s="99"/>
-      <c r="W2" s="99"/>
-      <c r="X2" s="99"/>
-      <c r="Y2" s="99"/>
-      <c r="Z2" s="99"/>
-      <c r="AA2" s="102"/>
-      <c r="AB2" s="102"/>
-      <c r="AC2" s="102"/>
-      <c r="AD2" s="102"/>
-      <c r="AE2" s="102"/>
+      <c r="A2" s="40"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="96"/>
+      <c r="K2" s="96"/>
+      <c r="L2" s="96"/>
+      <c r="M2" s="96"/>
+      <c r="N2" s="96"/>
+      <c r="O2" s="96"/>
+      <c r="P2" s="96"/>
+      <c r="Q2" s="96"/>
+      <c r="R2" s="96"/>
+      <c r="S2" s="96"/>
+      <c r="T2" s="96"/>
+      <c r="U2" s="96"/>
+      <c r="V2" s="96"/>
+      <c r="W2" s="96"/>
+      <c r="X2" s="96"/>
+      <c r="Y2" s="96"/>
+      <c r="Z2" s="96"/>
+      <c r="AA2" s="99"/>
+      <c r="AB2" s="99"/>
+      <c r="AC2" s="99"/>
+      <c r="AD2" s="99"/>
+      <c r="AE2" s="99"/>
       <c r="AF2" s="28"/>
-      <c r="AG2" s="52" t="s">
+      <c r="AG2" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="AH2" s="53"/>
-      <c r="AI2" s="53"/>
-      <c r="AJ2" s="53"/>
-      <c r="AK2" s="53"/>
-      <c r="AL2" s="53"/>
-      <c r="AM2" s="53"/>
-      <c r="AN2" s="54"/>
+      <c r="AH2" s="50"/>
+      <c r="AI2" s="50"/>
+      <c r="AJ2" s="50"/>
+      <c r="AK2" s="50"/>
+      <c r="AL2" s="50"/>
+      <c r="AM2" s="50"/>
+      <c r="AN2" s="51"/>
     </row>
     <row r="3" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43"/>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="55" t="s">
+      <c r="A3" s="40"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
-      <c r="L3" s="56"/>
-      <c r="M3" s="56"/>
-      <c r="N3" s="56"/>
-      <c r="O3" s="56"/>
-      <c r="P3" s="56"/>
-      <c r="Q3" s="56"/>
-      <c r="R3" s="56"/>
-      <c r="S3" s="56"/>
-      <c r="T3" s="56"/>
-      <c r="U3" s="56"/>
-      <c r="V3" s="56"/>
-      <c r="W3" s="56"/>
-      <c r="X3" s="56"/>
-      <c r="Y3" s="56"/>
-      <c r="Z3" s="56"/>
-      <c r="AA3" s="56"/>
-      <c r="AB3" s="56"/>
-      <c r="AC3" s="56"/>
-      <c r="AD3" s="56"/>
-      <c r="AE3" s="56"/>
-      <c r="AF3" s="57"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="53"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="53"/>
+      <c r="N3" s="53"/>
+      <c r="O3" s="53"/>
+      <c r="P3" s="53"/>
+      <c r="Q3" s="53"/>
+      <c r="R3" s="53"/>
+      <c r="S3" s="53"/>
+      <c r="T3" s="53"/>
+      <c r="U3" s="53"/>
+      <c r="V3" s="53"/>
+      <c r="W3" s="53"/>
+      <c r="X3" s="53"/>
+      <c r="Y3" s="53"/>
+      <c r="Z3" s="53"/>
+      <c r="AA3" s="53"/>
+      <c r="AB3" s="53"/>
+      <c r="AC3" s="53"/>
+      <c r="AD3" s="53"/>
+      <c r="AE3" s="53"/>
+      <c r="AF3" s="54"/>
       <c r="AG3" s="16" t="s">
         <v>3</v>
       </c>
@@ -2389,38 +2252,38 @@
       </c>
     </row>
     <row r="4" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="43"/>
-      <c r="B4" s="44"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="59"/>
-      <c r="K4" s="59"/>
-      <c r="L4" s="59"/>
-      <c r="M4" s="59"/>
-      <c r="N4" s="59"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="59"/>
-      <c r="Q4" s="59"/>
-      <c r="R4" s="59"/>
-      <c r="S4" s="59"/>
-      <c r="T4" s="59"/>
-      <c r="U4" s="59"/>
-      <c r="V4" s="59"/>
-      <c r="W4" s="59"/>
-      <c r="X4" s="59"/>
-      <c r="Y4" s="59"/>
-      <c r="Z4" s="59"/>
-      <c r="AA4" s="59"/>
-      <c r="AB4" s="59"/>
-      <c r="AC4" s="59"/>
-      <c r="AD4" s="59"/>
-      <c r="AE4" s="59"/>
-      <c r="AF4" s="60"/>
+      <c r="A4" s="40"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="56"/>
+      <c r="L4" s="56"/>
+      <c r="M4" s="56"/>
+      <c r="N4" s="56"/>
+      <c r="O4" s="56"/>
+      <c r="P4" s="56"/>
+      <c r="Q4" s="56"/>
+      <c r="R4" s="56"/>
+      <c r="S4" s="56"/>
+      <c r="T4" s="56"/>
+      <c r="U4" s="56"/>
+      <c r="V4" s="56"/>
+      <c r="W4" s="56"/>
+      <c r="X4" s="56"/>
+      <c r="Y4" s="56"/>
+      <c r="Z4" s="56"/>
+      <c r="AA4" s="56"/>
+      <c r="AB4" s="56"/>
+      <c r="AC4" s="56"/>
+      <c r="AD4" s="56"/>
+      <c r="AE4" s="56"/>
+      <c r="AF4" s="57"/>
       <c r="AG4" s="16" t="s">
         <v>7</v>
       </c>
@@ -2439,14 +2302,14 @@
       </c>
     </row>
     <row r="5" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="43"/>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="45"/>
+      <c r="A5" s="40"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="42"/>
       <c r="I5" s="19" t="s">
         <v>11</v>
       </c>
@@ -2491,14 +2354,14 @@
       </c>
     </row>
     <row r="6" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="43"/>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="45"/>
+      <c r="A6" s="40"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="42"/>
       <c r="I6" s="19" t="s">
         <v>15</v>
       </c>
@@ -2532,7 +2395,7 @@
       <c r="AC6" s="23"/>
       <c r="AD6" s="24"/>
       <c r="AE6" s="25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AF6" s="26"/>
       <c r="AG6" s="16" t="s">
@@ -2553,14 +2416,14 @@
       </c>
     </row>
     <row r="7" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="43"/>
-      <c r="B7" s="44"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="45"/>
+      <c r="A7" s="40"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="42"/>
       <c r="I7" s="19" t="s">
         <v>24</v>
       </c>
@@ -2570,7 +2433,7 @@
       <c r="M7" s="20"/>
       <c r="N7" s="21"/>
       <c r="O7" s="29" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P7" s="23"/>
       <c r="Q7" s="23"/>
@@ -2613,42 +2476,42 @@
       </c>
     </row>
     <row r="8" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="46"/>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="30" t="s">
+      <c r="A8" s="43"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="108" t="s">
         <v>32</v>
       </c>
-      <c r="J8" s="31"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="31"/>
-      <c r="M8" s="31"/>
-      <c r="N8" s="31"/>
-      <c r="O8" s="31"/>
-      <c r="P8" s="31"/>
-      <c r="Q8" s="31"/>
-      <c r="R8" s="31"/>
-      <c r="S8" s="31"/>
-      <c r="T8" s="32"/>
-      <c r="U8" s="30" t="s">
+      <c r="J8" s="109"/>
+      <c r="K8" s="109"/>
+      <c r="L8" s="109"/>
+      <c r="M8" s="109"/>
+      <c r="N8" s="109"/>
+      <c r="O8" s="109"/>
+      <c r="P8" s="109"/>
+      <c r="Q8" s="109"/>
+      <c r="R8" s="109"/>
+      <c r="S8" s="109"/>
+      <c r="T8" s="110"/>
+      <c r="U8" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="V8" s="31"/>
-      <c r="W8" s="31"/>
-      <c r="X8" s="31"/>
-      <c r="Y8" s="31"/>
-      <c r="Z8" s="31"/>
-      <c r="AA8" s="31"/>
-      <c r="AB8" s="31"/>
-      <c r="AC8" s="31"/>
-      <c r="AD8" s="31"/>
-      <c r="AE8" s="31"/>
-      <c r="AF8" s="32"/>
+      <c r="V8" s="111"/>
+      <c r="W8" s="111"/>
+      <c r="X8" s="111"/>
+      <c r="Y8" s="111"/>
+      <c r="Z8" s="111"/>
+      <c r="AA8" s="111"/>
+      <c r="AB8" s="111"/>
+      <c r="AC8" s="111"/>
+      <c r="AD8" s="111"/>
+      <c r="AE8" s="111"/>
+      <c r="AF8" s="112"/>
       <c r="AG8" s="16" t="s">
         <v>34</v>
       </c>
@@ -2667,7 +2530,7 @@
       </c>
     </row>
     <row r="9" spans="1:40" ht="12.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="30" t="s">
         <v>38</v>
       </c>
       <c r="B9" s="22" t="s">
@@ -2680,52 +2543,52 @@
       <c r="G9" s="23"/>
       <c r="H9" s="24"/>
       <c r="I9" s="3"/>
-      <c r="J9" s="35" t="s">
+      <c r="J9" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="K9" s="36"/>
-      <c r="L9" s="36"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="37"/>
-      <c r="Q9" s="35" t="s">
+      <c r="K9" s="33"/>
+      <c r="L9" s="33"/>
+      <c r="M9" s="33"/>
+      <c r="N9" s="33"/>
+      <c r="O9" s="33"/>
+      <c r="P9" s="34"/>
+      <c r="Q9" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="R9" s="36"/>
-      <c r="S9" s="36"/>
-      <c r="T9" s="37"/>
-      <c r="U9" s="38" t="s">
+      <c r="R9" s="33"/>
+      <c r="S9" s="33"/>
+      <c r="T9" s="34"/>
+      <c r="U9" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="V9" s="35" t="s">
+      <c r="V9" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="W9" s="36"/>
-      <c r="X9" s="36"/>
-      <c r="Y9" s="36"/>
-      <c r="Z9" s="36"/>
-      <c r="AA9" s="36"/>
-      <c r="AB9" s="37"/>
+      <c r="W9" s="33"/>
+      <c r="X9" s="33"/>
+      <c r="Y9" s="33"/>
+      <c r="Z9" s="33"/>
+      <c r="AA9" s="33"/>
+      <c r="AB9" s="34"/>
       <c r="AC9" s="3"/>
-      <c r="AD9" s="35" t="s">
+      <c r="AD9" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="AE9" s="36"/>
-      <c r="AF9" s="36"/>
-      <c r="AG9" s="36"/>
-      <c r="AH9" s="36"/>
-      <c r="AI9" s="36"/>
-      <c r="AJ9" s="37"/>
-      <c r="AK9" s="35" t="s">
+      <c r="AE9" s="33"/>
+      <c r="AF9" s="33"/>
+      <c r="AG9" s="33"/>
+      <c r="AH9" s="33"/>
+      <c r="AI9" s="33"/>
+      <c r="AJ9" s="34"/>
+      <c r="AK9" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="AL9" s="36"/>
-      <c r="AM9" s="36"/>
-      <c r="AN9" s="37"/>
+      <c r="AL9" s="33"/>
+      <c r="AM9" s="33"/>
+      <c r="AN9" s="34"/>
     </row>
     <row r="10" spans="1:40" ht="12.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="34"/>
+      <c r="A10" s="31"/>
       <c r="B10" s="19" t="s">
         <v>42</v>
       </c>
@@ -2738,18 +2601,18 @@
       <c r="I10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J10" s="35" t="s">
+      <c r="J10" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="K10" s="37"/>
-      <c r="L10" s="35" t="s">
+      <c r="K10" s="34"/>
+      <c r="L10" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="M10" s="37"/>
-      <c r="N10" s="35" t="s">
+      <c r="M10" s="34"/>
+      <c r="N10" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="O10" s="37"/>
+      <c r="O10" s="34"/>
       <c r="P10" s="1" t="s">
         <v>46</v>
       </c>
@@ -2765,7 +2628,7 @@
       <c r="T10" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="U10" s="39"/>
+      <c r="U10" s="36"/>
       <c r="V10" s="16" t="s">
         <v>47</v>
       </c>
@@ -2778,18 +2641,18 @@
       <c r="AC10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AD10" s="35" t="s">
+      <c r="AD10" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="AE10" s="37"/>
-      <c r="AF10" s="35" t="s">
+      <c r="AE10" s="34"/>
+      <c r="AF10" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="AG10" s="37"/>
-      <c r="AH10" s="35" t="s">
+      <c r="AG10" s="34"/>
+      <c r="AH10" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="AI10" s="37"/>
+      <c r="AI10" s="34"/>
       <c r="AJ10" s="1" t="s">
         <v>46</v>
       </c>
@@ -2810,13 +2673,13 @@
       <c r="A11" s="6">
         <v>1</v>
       </c>
-      <c r="B11" s="61"/>
-      <c r="C11" s="62"/>
-      <c r="D11" s="62"/>
-      <c r="E11" s="62"/>
-      <c r="F11" s="62"/>
-      <c r="G11" s="62"/>
-      <c r="H11" s="63"/>
+      <c r="B11" s="58"/>
+      <c r="C11" s="59"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="60"/>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
@@ -2832,13 +2695,13 @@
       <c r="U11" s="2">
         <v>1</v>
       </c>
-      <c r="V11" s="61"/>
-      <c r="W11" s="62"/>
-      <c r="X11" s="62"/>
-      <c r="Y11" s="62"/>
-      <c r="Z11" s="62"/>
-      <c r="AA11" s="62"/>
-      <c r="AB11" s="63"/>
+      <c r="V11" s="58"/>
+      <c r="W11" s="59"/>
+      <c r="X11" s="59"/>
+      <c r="Y11" s="59"/>
+      <c r="Z11" s="59"/>
+      <c r="AA11" s="59"/>
+      <c r="AB11" s="60"/>
       <c r="AC11" s="4"/>
       <c r="AD11" s="4"/>
       <c r="AE11" s="4"/>
@@ -2856,13 +2719,13 @@
       <c r="A12" s="6">
         <v>2</v>
       </c>
-      <c r="B12" s="61"/>
-      <c r="C12" s="62"/>
-      <c r="D12" s="62"/>
-      <c r="E12" s="62"/>
-      <c r="F12" s="62"/>
-      <c r="G12" s="62"/>
-      <c r="H12" s="63"/>
+      <c r="B12" s="58"/>
+      <c r="C12" s="59"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="60"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
@@ -2878,13 +2741,13 @@
       <c r="U12" s="2">
         <v>2</v>
       </c>
-      <c r="V12" s="61"/>
-      <c r="W12" s="62"/>
-      <c r="X12" s="62"/>
-      <c r="Y12" s="62"/>
-      <c r="Z12" s="62"/>
-      <c r="AA12" s="62"/>
-      <c r="AB12" s="63"/>
+      <c r="V12" s="58"/>
+      <c r="W12" s="59"/>
+      <c r="X12" s="59"/>
+      <c r="Y12" s="59"/>
+      <c r="Z12" s="59"/>
+      <c r="AA12" s="59"/>
+      <c r="AB12" s="60"/>
       <c r="AC12" s="4"/>
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
@@ -2902,13 +2765,13 @@
       <c r="A13" s="6">
         <v>3</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="62"/>
-      <c r="D13" s="62"/>
-      <c r="E13" s="62"/>
-      <c r="F13" s="62"/>
-      <c r="G13" s="62"/>
-      <c r="H13" s="63"/>
+      <c r="B13" s="58"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="59"/>
+      <c r="H13" s="60"/>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
@@ -2924,13 +2787,13 @@
       <c r="U13" s="2">
         <v>3</v>
       </c>
-      <c r="V13" s="61"/>
-      <c r="W13" s="62"/>
-      <c r="X13" s="62"/>
-      <c r="Y13" s="62"/>
-      <c r="Z13" s="62"/>
-      <c r="AA13" s="62"/>
-      <c r="AB13" s="63"/>
+      <c r="V13" s="58"/>
+      <c r="W13" s="59"/>
+      <c r="X13" s="59"/>
+      <c r="Y13" s="59"/>
+      <c r="Z13" s="59"/>
+      <c r="AA13" s="59"/>
+      <c r="AB13" s="60"/>
       <c r="AC13" s="4"/>
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
@@ -2948,13 +2811,13 @@
       <c r="A14" s="6">
         <v>4</v>
       </c>
-      <c r="B14" s="61"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="63"/>
+      <c r="B14" s="58"/>
+      <c r="C14" s="59"/>
+      <c r="D14" s="59"/>
+      <c r="E14" s="59"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="59"/>
+      <c r="H14" s="60"/>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
@@ -2970,13 +2833,13 @@
       <c r="U14" s="2">
         <v>4</v>
       </c>
-      <c r="V14" s="61"/>
-      <c r="W14" s="62"/>
-      <c r="X14" s="62"/>
-      <c r="Y14" s="62"/>
-      <c r="Z14" s="62"/>
-      <c r="AA14" s="62"/>
-      <c r="AB14" s="63"/>
+      <c r="V14" s="58"/>
+      <c r="W14" s="59"/>
+      <c r="X14" s="59"/>
+      <c r="Y14" s="59"/>
+      <c r="Z14" s="59"/>
+      <c r="AA14" s="59"/>
+      <c r="AB14" s="60"/>
       <c r="AC14" s="4"/>
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
@@ -2994,13 +2857,13 @@
       <c r="A15" s="6">
         <v>5</v>
       </c>
-      <c r="B15" s="61"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="62"/>
-      <c r="E15" s="62"/>
-      <c r="F15" s="62"/>
-      <c r="G15" s="62"/>
-      <c r="H15" s="63"/>
+      <c r="B15" s="58"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="59"/>
+      <c r="E15" s="59"/>
+      <c r="F15" s="59"/>
+      <c r="G15" s="59"/>
+      <c r="H15" s="60"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
@@ -3016,13 +2879,13 @@
       <c r="U15" s="2">
         <v>5</v>
       </c>
-      <c r="V15" s="61"/>
-      <c r="W15" s="62"/>
-      <c r="X15" s="62"/>
-      <c r="Y15" s="62"/>
-      <c r="Z15" s="62"/>
-      <c r="AA15" s="62"/>
-      <c r="AB15" s="63"/>
+      <c r="V15" s="58"/>
+      <c r="W15" s="59"/>
+      <c r="X15" s="59"/>
+      <c r="Y15" s="59"/>
+      <c r="Z15" s="59"/>
+      <c r="AA15" s="59"/>
+      <c r="AB15" s="60"/>
       <c r="AC15" s="4"/>
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
@@ -3040,13 +2903,13 @@
       <c r="A16" s="6">
         <v>6</v>
       </c>
-      <c r="B16" s="61"/>
-      <c r="C16" s="62"/>
-      <c r="D16" s="62"/>
-      <c r="E16" s="62"/>
-      <c r="F16" s="62"/>
-      <c r="G16" s="62"/>
-      <c r="H16" s="63"/>
+      <c r="B16" s="58"/>
+      <c r="C16" s="59"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="59"/>
+      <c r="H16" s="60"/>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
@@ -3062,13 +2925,13 @@
       <c r="U16" s="2">
         <v>6</v>
       </c>
-      <c r="V16" s="61"/>
-      <c r="W16" s="62"/>
-      <c r="X16" s="62"/>
-      <c r="Y16" s="62"/>
-      <c r="Z16" s="62"/>
-      <c r="AA16" s="62"/>
-      <c r="AB16" s="63"/>
+      <c r="V16" s="58"/>
+      <c r="W16" s="59"/>
+      <c r="X16" s="59"/>
+      <c r="Y16" s="59"/>
+      <c r="Z16" s="59"/>
+      <c r="AA16" s="59"/>
+      <c r="AB16" s="60"/>
       <c r="AC16" s="4"/>
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
@@ -3086,13 +2949,13 @@
       <c r="A17" s="6">
         <v>7</v>
       </c>
-      <c r="B17" s="61"/>
-      <c r="C17" s="62"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="62"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="63"/>
+      <c r="B17" s="58"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="59"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="60"/>
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
@@ -3108,13 +2971,13 @@
       <c r="U17" s="2">
         <v>7</v>
       </c>
-      <c r="V17" s="61"/>
-      <c r="W17" s="62"/>
-      <c r="X17" s="62"/>
-      <c r="Y17" s="62"/>
-      <c r="Z17" s="62"/>
-      <c r="AA17" s="62"/>
-      <c r="AB17" s="63"/>
+      <c r="V17" s="58"/>
+      <c r="W17" s="59"/>
+      <c r="X17" s="59"/>
+      <c r="Y17" s="59"/>
+      <c r="Z17" s="59"/>
+      <c r="AA17" s="59"/>
+      <c r="AB17" s="60"/>
       <c r="AC17" s="4"/>
       <c r="AD17" s="4"/>
       <c r="AE17" s="4"/>
@@ -3132,13 +2995,13 @@
       <c r="A18" s="6">
         <v>8</v>
       </c>
-      <c r="B18" s="61"/>
-      <c r="C18" s="62"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="62"/>
-      <c r="F18" s="62"/>
-      <c r="G18" s="62"/>
-      <c r="H18" s="63"/>
+      <c r="B18" s="58"/>
+      <c r="C18" s="59"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="59"/>
+      <c r="H18" s="60"/>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
@@ -3154,13 +3017,13 @@
       <c r="U18" s="2">
         <v>8</v>
       </c>
-      <c r="V18" s="61"/>
-      <c r="W18" s="62"/>
-      <c r="X18" s="62"/>
-      <c r="Y18" s="62"/>
-      <c r="Z18" s="62"/>
-      <c r="AA18" s="62"/>
-      <c r="AB18" s="63"/>
+      <c r="V18" s="58"/>
+      <c r="W18" s="59"/>
+      <c r="X18" s="59"/>
+      <c r="Y18" s="59"/>
+      <c r="Z18" s="59"/>
+      <c r="AA18" s="59"/>
+      <c r="AB18" s="60"/>
       <c r="AC18" s="4"/>
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
@@ -3178,13 +3041,13 @@
       <c r="A19" s="6">
         <v>9</v>
       </c>
-      <c r="B19" s="61"/>
-      <c r="C19" s="62"/>
-      <c r="D19" s="62"/>
-      <c r="E19" s="62"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="62"/>
-      <c r="H19" s="63"/>
+      <c r="B19" s="58"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="60"/>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
@@ -3200,13 +3063,13 @@
       <c r="U19" s="2">
         <v>9</v>
       </c>
-      <c r="V19" s="61"/>
-      <c r="W19" s="62"/>
-      <c r="X19" s="62"/>
-      <c r="Y19" s="62"/>
-      <c r="Z19" s="62"/>
-      <c r="AA19" s="62"/>
-      <c r="AB19" s="63"/>
+      <c r="V19" s="58"/>
+      <c r="W19" s="59"/>
+      <c r="X19" s="59"/>
+      <c r="Y19" s="59"/>
+      <c r="Z19" s="59"/>
+      <c r="AA19" s="59"/>
+      <c r="AB19" s="60"/>
       <c r="AC19" s="4"/>
       <c r="AD19" s="4"/>
       <c r="AE19" s="4"/>
@@ -3224,13 +3087,13 @@
       <c r="A20" s="6">
         <v>10</v>
       </c>
-      <c r="B20" s="61"/>
-      <c r="C20" s="62"/>
-      <c r="D20" s="62"/>
-      <c r="E20" s="62"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="62"/>
-      <c r="H20" s="63"/>
+      <c r="B20" s="58"/>
+      <c r="C20" s="59"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="59"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="59"/>
+      <c r="H20" s="60"/>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
@@ -3246,13 +3109,13 @@
       <c r="U20" s="2">
         <v>10</v>
       </c>
-      <c r="V20" s="61"/>
-      <c r="W20" s="62"/>
-      <c r="X20" s="62"/>
-      <c r="Y20" s="62"/>
-      <c r="Z20" s="62"/>
-      <c r="AA20" s="62"/>
-      <c r="AB20" s="63"/>
+      <c r="V20" s="58"/>
+      <c r="W20" s="59"/>
+      <c r="X20" s="59"/>
+      <c r="Y20" s="59"/>
+      <c r="Z20" s="59"/>
+      <c r="AA20" s="59"/>
+      <c r="AB20" s="60"/>
       <c r="AC20" s="4"/>
       <c r="AD20" s="4"/>
       <c r="AE20" s="4"/>
@@ -3270,13 +3133,13 @@
       <c r="A21" s="6">
         <v>11</v>
       </c>
-      <c r="B21" s="61"/>
-      <c r="C21" s="62"/>
-      <c r="D21" s="62"/>
-      <c r="E21" s="62"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="63"/>
+      <c r="B21" s="58"/>
+      <c r="C21" s="59"/>
+      <c r="D21" s="59"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="59"/>
+      <c r="G21" s="59"/>
+      <c r="H21" s="60"/>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
@@ -3292,13 +3155,13 @@
       <c r="U21" s="2">
         <v>11</v>
       </c>
-      <c r="V21" s="61"/>
-      <c r="W21" s="62"/>
-      <c r="X21" s="62"/>
-      <c r="Y21" s="62"/>
-      <c r="Z21" s="62"/>
-      <c r="AA21" s="62"/>
-      <c r="AB21" s="63"/>
+      <c r="V21" s="58"/>
+      <c r="W21" s="59"/>
+      <c r="X21" s="59"/>
+      <c r="Y21" s="59"/>
+      <c r="Z21" s="59"/>
+      <c r="AA21" s="59"/>
+      <c r="AB21" s="60"/>
       <c r="AC21" s="4"/>
       <c r="AD21" s="4"/>
       <c r="AE21" s="4"/>
@@ -3316,13 +3179,13 @@
       <c r="A22" s="6">
         <v>12</v>
       </c>
-      <c r="B22" s="61"/>
-      <c r="C22" s="62"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="62"/>
-      <c r="H22" s="63"/>
+      <c r="B22" s="58"/>
+      <c r="C22" s="59"/>
+      <c r="D22" s="59"/>
+      <c r="E22" s="59"/>
+      <c r="F22" s="59"/>
+      <c r="G22" s="59"/>
+      <c r="H22" s="60"/>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
@@ -3338,13 +3201,13 @@
       <c r="U22" s="2">
         <v>12</v>
       </c>
-      <c r="V22" s="61"/>
-      <c r="W22" s="62"/>
-      <c r="X22" s="62"/>
-      <c r="Y22" s="62"/>
-      <c r="Z22" s="62"/>
-      <c r="AA22" s="62"/>
-      <c r="AB22" s="63"/>
+      <c r="V22" s="58"/>
+      <c r="W22" s="59"/>
+      <c r="X22" s="59"/>
+      <c r="Y22" s="59"/>
+      <c r="Z22" s="59"/>
+      <c r="AA22" s="59"/>
+      <c r="AB22" s="60"/>
       <c r="AC22" s="4"/>
       <c r="AD22" s="4"/>
       <c r="AE22" s="4"/>
@@ -3362,13 +3225,13 @@
       <c r="A23" s="6">
         <v>13</v>
       </c>
-      <c r="B23" s="61"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="63"/>
+      <c r="B23" s="58"/>
+      <c r="C23" s="59"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="59"/>
+      <c r="G23" s="59"/>
+      <c r="H23" s="60"/>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
@@ -3384,13 +3247,13 @@
       <c r="U23" s="2">
         <v>13</v>
       </c>
-      <c r="V23" s="61"/>
-      <c r="W23" s="62"/>
-      <c r="X23" s="62"/>
-      <c r="Y23" s="62"/>
-      <c r="Z23" s="62"/>
-      <c r="AA23" s="62"/>
-      <c r="AB23" s="63"/>
+      <c r="V23" s="58"/>
+      <c r="W23" s="59"/>
+      <c r="X23" s="59"/>
+      <c r="Y23" s="59"/>
+      <c r="Z23" s="59"/>
+      <c r="AA23" s="59"/>
+      <c r="AB23" s="60"/>
       <c r="AC23" s="4"/>
       <c r="AD23" s="4"/>
       <c r="AE23" s="4"/>
@@ -3408,13 +3271,13 @@
       <c r="A24" s="6">
         <v>14</v>
       </c>
-      <c r="B24" s="61"/>
-      <c r="C24" s="62"/>
-      <c r="D24" s="62"/>
-      <c r="E24" s="62"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="62"/>
-      <c r="H24" s="63"/>
+      <c r="B24" s="58"/>
+      <c r="C24" s="59"/>
+      <c r="D24" s="59"/>
+      <c r="E24" s="59"/>
+      <c r="F24" s="59"/>
+      <c r="G24" s="59"/>
+      <c r="H24" s="60"/>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
@@ -3430,13 +3293,13 @@
       <c r="U24" s="2">
         <v>14</v>
       </c>
-      <c r="V24" s="61"/>
-      <c r="W24" s="62"/>
-      <c r="X24" s="62"/>
-      <c r="Y24" s="62"/>
-      <c r="Z24" s="62"/>
-      <c r="AA24" s="62"/>
-      <c r="AB24" s="63"/>
+      <c r="V24" s="58"/>
+      <c r="W24" s="59"/>
+      <c r="X24" s="59"/>
+      <c r="Y24" s="59"/>
+      <c r="Z24" s="59"/>
+      <c r="AA24" s="59"/>
+      <c r="AB24" s="60"/>
       <c r="AC24" s="4"/>
       <c r="AD24" s="4"/>
       <c r="AE24" s="4"/>
@@ -3454,13 +3317,13 @@
       <c r="A25" s="6">
         <v>15</v>
       </c>
-      <c r="B25" s="61"/>
-      <c r="C25" s="62"/>
-      <c r="D25" s="62"/>
-      <c r="E25" s="62"/>
-      <c r="F25" s="62"/>
-      <c r="G25" s="62"/>
-      <c r="H25" s="63"/>
+      <c r="B25" s="58"/>
+      <c r="C25" s="59"/>
+      <c r="D25" s="59"/>
+      <c r="E25" s="59"/>
+      <c r="F25" s="59"/>
+      <c r="G25" s="59"/>
+      <c r="H25" s="60"/>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
@@ -3476,13 +3339,13 @@
       <c r="U25" s="2">
         <v>15</v>
       </c>
-      <c r="V25" s="61"/>
-      <c r="W25" s="62"/>
-      <c r="X25" s="62"/>
-      <c r="Y25" s="62"/>
-      <c r="Z25" s="62"/>
-      <c r="AA25" s="62"/>
-      <c r="AB25" s="63"/>
+      <c r="V25" s="58"/>
+      <c r="W25" s="59"/>
+      <c r="X25" s="59"/>
+      <c r="Y25" s="59"/>
+      <c r="Z25" s="59"/>
+      <c r="AA25" s="59"/>
+      <c r="AB25" s="60"/>
       <c r="AC25" s="4"/>
       <c r="AD25" s="4"/>
       <c r="AE25" s="4"/>
@@ -3508,19 +3371,19 @@
       <c r="G26" s="20"/>
       <c r="H26" s="21"/>
       <c r="I26" s="4"/>
-      <c r="J26" s="35" t="s">
+      <c r="J26" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="K26" s="36"/>
-      <c r="L26" s="36"/>
-      <c r="M26" s="36"/>
-      <c r="N26" s="36"/>
-      <c r="O26" s="36"/>
-      <c r="P26" s="36"/>
-      <c r="Q26" s="36"/>
-      <c r="R26" s="36"/>
-      <c r="S26" s="36"/>
-      <c r="T26" s="37"/>
+      <c r="K26" s="23"/>
+      <c r="L26" s="23"/>
+      <c r="M26" s="23"/>
+      <c r="N26" s="23"/>
+      <c r="O26" s="23"/>
+      <c r="P26" s="23"/>
+      <c r="Q26" s="23"/>
+      <c r="R26" s="23"/>
+      <c r="S26" s="23"/>
+      <c r="T26" s="24"/>
       <c r="U26" s="16" t="s">
         <v>48</v>
       </c>
@@ -3532,19 +3395,19 @@
       <c r="AA26" s="17"/>
       <c r="AB26" s="18"/>
       <c r="AC26" s="4"/>
-      <c r="AD26" s="35" t="s">
+      <c r="AD26" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="AE26" s="36"/>
-      <c r="AF26" s="36"/>
-      <c r="AG26" s="36"/>
-      <c r="AH26" s="36"/>
-      <c r="AI26" s="36"/>
-      <c r="AJ26" s="36"/>
-      <c r="AK26" s="36"/>
-      <c r="AL26" s="36"/>
-      <c r="AM26" s="36"/>
-      <c r="AN26" s="37"/>
+      <c r="AE26" s="23"/>
+      <c r="AF26" s="23"/>
+      <c r="AG26" s="23"/>
+      <c r="AH26" s="23"/>
+      <c r="AI26" s="23"/>
+      <c r="AJ26" s="23"/>
+      <c r="AK26" s="23"/>
+      <c r="AL26" s="23"/>
+      <c r="AM26" s="23"/>
+      <c r="AN26" s="24"/>
     </row>
     <row r="27" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
@@ -3701,74 +3564,74 @@
       <c r="AN29" s="24"/>
     </row>
     <row r="30" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="67"/>
-      <c r="B30" s="68"/>
-      <c r="C30" s="67"/>
-      <c r="D30" s="73"/>
-      <c r="E30" s="68"/>
-      <c r="F30" s="67"/>
-      <c r="G30" s="73"/>
-      <c r="H30" s="68"/>
-      <c r="I30" s="67"/>
-      <c r="J30" s="68"/>
-      <c r="K30" s="64" t="s">
+      <c r="A30" s="64"/>
+      <c r="B30" s="65"/>
+      <c r="C30" s="64"/>
+      <c r="D30" s="70"/>
+      <c r="E30" s="65"/>
+      <c r="F30" s="64"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="65"/>
+      <c r="I30" s="64"/>
+      <c r="J30" s="65"/>
+      <c r="K30" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="L30" s="65"/>
-      <c r="M30" s="66"/>
-      <c r="N30" s="64" t="s">
+      <c r="L30" s="62"/>
+      <c r="M30" s="63"/>
+      <c r="N30" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="O30" s="65"/>
-      <c r="P30" s="66"/>
-      <c r="Q30" s="64" t="s">
+      <c r="O30" s="62"/>
+      <c r="P30" s="63"/>
+      <c r="Q30" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="R30" s="65"/>
-      <c r="S30" s="66"/>
+      <c r="R30" s="62"/>
+      <c r="S30" s="63"/>
       <c r="T30" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="U30" s="67"/>
-      <c r="V30" s="68"/>
-      <c r="W30" s="67"/>
-      <c r="X30" s="73"/>
-      <c r="Y30" s="68"/>
-      <c r="Z30" s="67"/>
-      <c r="AA30" s="73"/>
-      <c r="AB30" s="68"/>
-      <c r="AC30" s="67"/>
-      <c r="AD30" s="68"/>
-      <c r="AE30" s="64" t="s">
+      <c r="U30" s="64"/>
+      <c r="V30" s="65"/>
+      <c r="W30" s="64"/>
+      <c r="X30" s="70"/>
+      <c r="Y30" s="65"/>
+      <c r="Z30" s="64"/>
+      <c r="AA30" s="70"/>
+      <c r="AB30" s="65"/>
+      <c r="AC30" s="64"/>
+      <c r="AD30" s="65"/>
+      <c r="AE30" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="AF30" s="65"/>
-      <c r="AG30" s="66"/>
-      <c r="AH30" s="64" t="s">
+      <c r="AF30" s="62"/>
+      <c r="AG30" s="63"/>
+      <c r="AH30" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="AI30" s="65"/>
-      <c r="AJ30" s="66"/>
-      <c r="AK30" s="64" t="s">
+      <c r="AI30" s="62"/>
+      <c r="AJ30" s="63"/>
+      <c r="AK30" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="AL30" s="65"/>
-      <c r="AM30" s="66"/>
+      <c r="AL30" s="62"/>
+      <c r="AM30" s="63"/>
       <c r="AN30" s="7" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:40" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="69"/>
-      <c r="B31" s="70"/>
-      <c r="C31" s="69"/>
-      <c r="D31" s="74"/>
-      <c r="E31" s="70"/>
-      <c r="F31" s="69"/>
-      <c r="G31" s="74"/>
-      <c r="H31" s="70"/>
-      <c r="I31" s="69"/>
-      <c r="J31" s="74"/>
+      <c r="A31" s="66"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="66"/>
+      <c r="D31" s="71"/>
+      <c r="E31" s="67"/>
+      <c r="F31" s="66"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="67"/>
+      <c r="I31" s="66"/>
+      <c r="J31" s="71"/>
       <c r="K31" s="13"/>
       <c r="L31" s="13"/>
       <c r="M31" s="13"/>
@@ -3779,16 +3642,16 @@
       <c r="R31" s="13"/>
       <c r="S31" s="13"/>
       <c r="T31" s="13"/>
-      <c r="U31" s="74"/>
-      <c r="V31" s="70"/>
-      <c r="W31" s="69"/>
-      <c r="X31" s="74"/>
-      <c r="Y31" s="70"/>
-      <c r="Z31" s="69"/>
-      <c r="AA31" s="74"/>
-      <c r="AB31" s="70"/>
-      <c r="AC31" s="69"/>
-      <c r="AD31" s="74"/>
+      <c r="U31" s="71"/>
+      <c r="V31" s="67"/>
+      <c r="W31" s="66"/>
+      <c r="X31" s="71"/>
+      <c r="Y31" s="67"/>
+      <c r="Z31" s="66"/>
+      <c r="AA31" s="71"/>
+      <c r="AB31" s="67"/>
+      <c r="AC31" s="66"/>
+      <c r="AD31" s="71"/>
       <c r="AE31" s="13"/>
       <c r="AF31" s="13"/>
       <c r="AG31" s="13"/>
@@ -3801,16 +3664,16 @@
       <c r="AN31" s="13"/>
     </row>
     <row r="32" spans="1:40" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="71"/>
-      <c r="B32" s="72"/>
-      <c r="C32" s="71"/>
-      <c r="D32" s="75"/>
-      <c r="E32" s="72"/>
-      <c r="F32" s="71"/>
-      <c r="G32" s="75"/>
-      <c r="H32" s="72"/>
-      <c r="I32" s="71"/>
-      <c r="J32" s="75"/>
+      <c r="A32" s="68"/>
+      <c r="B32" s="69"/>
+      <c r="C32" s="68"/>
+      <c r="D32" s="72"/>
+      <c r="E32" s="69"/>
+      <c r="F32" s="68"/>
+      <c r="G32" s="72"/>
+      <c r="H32" s="69"/>
+      <c r="I32" s="68"/>
+      <c r="J32" s="72"/>
       <c r="K32" s="14"/>
       <c r="L32" s="14"/>
       <c r="M32" s="14"/>
@@ -3821,16 +3684,16 @@
       <c r="R32" s="14"/>
       <c r="S32" s="14"/>
       <c r="T32" s="14"/>
-      <c r="U32" s="75"/>
-      <c r="V32" s="72"/>
-      <c r="W32" s="71"/>
-      <c r="X32" s="75"/>
-      <c r="Y32" s="72"/>
-      <c r="Z32" s="71"/>
-      <c r="AA32" s="75"/>
-      <c r="AB32" s="72"/>
-      <c r="AC32" s="71"/>
-      <c r="AD32" s="75"/>
+      <c r="U32" s="72"/>
+      <c r="V32" s="69"/>
+      <c r="W32" s="68"/>
+      <c r="X32" s="72"/>
+      <c r="Y32" s="69"/>
+      <c r="Z32" s="68"/>
+      <c r="AA32" s="72"/>
+      <c r="AB32" s="69"/>
+      <c r="AC32" s="68"/>
+      <c r="AD32" s="72"/>
       <c r="AE32" s="15"/>
       <c r="AF32" s="15"/>
       <c r="AG32" s="15"/>
@@ -3843,18 +3706,18 @@
       <c r="AN32" s="15"/>
     </row>
     <row r="33" spans="1:40" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="76" t="s">
+      <c r="A33" s="73" t="s">
         <v>62</v>
       </c>
-      <c r="B33" s="77"/>
-      <c r="C33" s="77"/>
-      <c r="D33" s="77"/>
-      <c r="E33" s="77"/>
-      <c r="F33" s="77"/>
-      <c r="G33" s="77"/>
-      <c r="H33" s="77"/>
-      <c r="I33" s="77"/>
-      <c r="J33" s="77"/>
+      <c r="B33" s="74"/>
+      <c r="C33" s="74"/>
+      <c r="D33" s="74"/>
+      <c r="E33" s="74"/>
+      <c r="F33" s="74"/>
+      <c r="G33" s="74"/>
+      <c r="H33" s="74"/>
+      <c r="I33" s="74"/>
+      <c r="J33" s="74"/>
       <c r="K33" s="14"/>
       <c r="L33" s="14"/>
       <c r="M33" s="14"/>
@@ -3865,18 +3728,18 @@
       <c r="R33" s="14"/>
       <c r="S33" s="14"/>
       <c r="T33" s="14"/>
-      <c r="U33" s="77" t="s">
+      <c r="U33" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="V33" s="77"/>
-      <c r="W33" s="77"/>
-      <c r="X33" s="77"/>
-      <c r="Y33" s="77"/>
-      <c r="Z33" s="77"/>
-      <c r="AA33" s="77"/>
-      <c r="AB33" s="77"/>
-      <c r="AC33" s="77"/>
-      <c r="AD33" s="77"/>
+      <c r="V33" s="74"/>
+      <c r="W33" s="74"/>
+      <c r="X33" s="74"/>
+      <c r="Y33" s="74"/>
+      <c r="Z33" s="74"/>
+      <c r="AA33" s="74"/>
+      <c r="AB33" s="74"/>
+      <c r="AC33" s="74"/>
+      <c r="AD33" s="74"/>
       <c r="AE33" s="15"/>
       <c r="AF33" s="15"/>
       <c r="AG33" s="15"/>
@@ -3889,10 +3752,10 @@
       <c r="AN33" s="15"/>
     </row>
     <row r="34" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="78" t="s">
+      <c r="A34" s="75" t="s">
         <v>64</v>
       </c>
-      <c r="B34" s="78"/>
+      <c r="B34" s="75"/>
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
@@ -3911,10 +3774,10 @@
       <c r="R34" s="12"/>
       <c r="S34" s="10"/>
       <c r="T34" s="10"/>
-      <c r="U34" s="79" t="s">
+      <c r="U34" s="76" t="s">
         <v>65</v>
       </c>
-      <c r="V34" s="79"/>
+      <c r="V34" s="76"/>
       <c r="W34" s="5"/>
       <c r="X34" s="5"/>
       <c r="Y34" s="5"/>
@@ -3935,10 +3798,10 @@
       <c r="AN34" s="5"/>
     </row>
     <row r="35" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="78" t="s">
+      <c r="A35" s="75" t="s">
         <v>66</v>
       </c>
-      <c r="B35" s="78"/>
+      <c r="B35" s="75"/>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
@@ -3957,10 +3820,10 @@
       <c r="R35" s="9"/>
       <c r="S35" s="5"/>
       <c r="T35" s="5"/>
-      <c r="U35" s="79" t="s">
+      <c r="U35" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="V35" s="79"/>
+      <c r="V35" s="76"/>
       <c r="W35" s="5"/>
       <c r="X35" s="5"/>
       <c r="Y35" s="5"/>
@@ -3981,10 +3844,10 @@
       <c r="AN35" s="5"/>
     </row>
     <row r="36" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="78" t="s">
+      <c r="A36" s="75" t="s">
         <v>68</v>
       </c>
-      <c r="B36" s="78"/>
+      <c r="B36" s="75"/>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
@@ -4003,10 +3866,10 @@
       <c r="R36" s="9"/>
       <c r="S36" s="5"/>
       <c r="T36" s="5"/>
-      <c r="U36" s="79" t="s">
+      <c r="U36" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="V36" s="79"/>
+      <c r="V36" s="76"/>
       <c r="W36" s="5"/>
       <c r="X36" s="5"/>
       <c r="Y36" s="5"/>
@@ -4027,10 +3890,10 @@
       <c r="AN36" s="5"/>
     </row>
     <row r="37" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="78" t="s">
+      <c r="A37" s="75" t="s">
         <v>69</v>
       </c>
-      <c r="B37" s="78"/>
+      <c r="B37" s="75"/>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
@@ -4049,10 +3912,10 @@
       <c r="R37" s="9"/>
       <c r="S37" s="5"/>
       <c r="T37" s="5"/>
-      <c r="U37" s="79" t="s">
+      <c r="U37" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="V37" s="79"/>
+      <c r="V37" s="76"/>
       <c r="W37" s="5"/>
       <c r="X37" s="5"/>
       <c r="Y37" s="5"/>
@@ -4073,10 +3936,10 @@
       <c r="AN37" s="5"/>
     </row>
     <row r="38" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="78" t="s">
+      <c r="A38" s="75" t="s">
         <v>70</v>
       </c>
-      <c r="B38" s="78"/>
+      <c r="B38" s="75"/>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
@@ -4095,10 +3958,10 @@
       <c r="R38" s="9"/>
       <c r="S38" s="5"/>
       <c r="T38" s="5"/>
-      <c r="U38" s="79" t="s">
+      <c r="U38" s="76" t="s">
         <v>70</v>
       </c>
-      <c r="V38" s="79"/>
+      <c r="V38" s="76"/>
       <c r="W38" s="5"/>
       <c r="X38" s="5"/>
       <c r="Y38" s="5"/>
@@ -4119,10 +3982,10 @@
       <c r="AN38" s="5"/>
     </row>
     <row r="39" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="79" t="s">
+      <c r="A39" s="76" t="s">
         <v>64</v>
       </c>
-      <c r="B39" s="79"/>
+      <c r="B39" s="76"/>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
@@ -4141,10 +4004,10 @@
       <c r="R39" s="5"/>
       <c r="S39" s="5"/>
       <c r="T39" s="5"/>
-      <c r="U39" s="79" t="s">
+      <c r="U39" s="76" t="s">
         <v>65</v>
       </c>
-      <c r="V39" s="79"/>
+      <c r="V39" s="76"/>
       <c r="W39" s="5"/>
       <c r="X39" s="5"/>
       <c r="Y39" s="5"/>
@@ -4165,10 +4028,10 @@
       <c r="AN39" s="5"/>
     </row>
     <row r="40" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="79" t="s">
+      <c r="A40" s="76" t="s">
         <v>66</v>
       </c>
-      <c r="B40" s="79"/>
+      <c r="B40" s="76"/>
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
@@ -4187,10 +4050,10 @@
       <c r="R40" s="5"/>
       <c r="S40" s="5"/>
       <c r="T40" s="5"/>
-      <c r="U40" s="79" t="s">
+      <c r="U40" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="V40" s="79"/>
+      <c r="V40" s="76"/>
       <c r="W40" s="5"/>
       <c r="X40" s="5"/>
       <c r="Y40" s="5"/>
@@ -4211,10 +4074,10 @@
       <c r="AN40" s="5"/>
     </row>
     <row r="41" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="79" t="s">
+      <c r="A41" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="B41" s="79"/>
+      <c r="B41" s="76"/>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
@@ -4233,10 +4096,10 @@
       <c r="R41" s="5"/>
       <c r="S41" s="5"/>
       <c r="T41" s="5"/>
-      <c r="U41" s="79" t="s">
+      <c r="U41" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="V41" s="79"/>
+      <c r="V41" s="76"/>
       <c r="W41" s="5"/>
       <c r="X41" s="5"/>
       <c r="Y41" s="5"/>
@@ -4257,10 +4120,10 @@
       <c r="AN41" s="5"/>
     </row>
     <row r="42" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="79" t="s">
+      <c r="A42" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="B42" s="79"/>
+      <c r="B42" s="76"/>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
@@ -4279,10 +4142,10 @@
       <c r="R42" s="5"/>
       <c r="S42" s="5"/>
       <c r="T42" s="5"/>
-      <c r="U42" s="79" t="s">
+      <c r="U42" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="V42" s="79"/>
+      <c r="V42" s="76"/>
       <c r="W42" s="5"/>
       <c r="X42" s="5"/>
       <c r="Y42" s="5"/>
@@ -4303,10 +4166,10 @@
       <c r="AN42" s="5"/>
     </row>
     <row r="43" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="79" t="s">
+      <c r="A43" s="76" t="s">
         <v>70</v>
       </c>
-      <c r="B43" s="79"/>
+      <c r="B43" s="76"/>
       <c r="C43" s="5"/>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
@@ -4325,10 +4188,10 @@
       <c r="R43" s="5"/>
       <c r="S43" s="5"/>
       <c r="T43" s="5"/>
-      <c r="U43" s="79" t="s">
+      <c r="U43" s="76" t="s">
         <v>70</v>
       </c>
-      <c r="V43" s="79"/>
+      <c r="V43" s="76"/>
       <c r="W43" s="5"/>
       <c r="X43" s="5"/>
       <c r="Y43" s="5"/>
@@ -4349,164 +4212,164 @@
       <c r="AN43" s="5"/>
     </row>
     <row r="44" spans="1:40" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="71" t="s">
+      <c r="A44" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="B44" s="28"/>
+      <c r="C44" s="77" t="s">
+        <v>89</v>
+      </c>
+      <c r="D44" s="78"/>
+      <c r="E44" s="77" t="s">
+        <v>90</v>
+      </c>
+      <c r="F44" s="78"/>
+      <c r="G44" s="77" t="s">
+        <v>91</v>
+      </c>
+      <c r="H44" s="78"/>
+      <c r="I44" s="77" t="s">
+        <v>92</v>
+      </c>
+      <c r="J44" s="78"/>
+      <c r="K44" s="79" t="s">
         <v>71</v>
       </c>
-      <c r="B44" s="72"/>
-      <c r="C44" s="80" t="s">
-        <v>43</v>
-      </c>
-      <c r="D44" s="81"/>
-      <c r="E44" s="80" t="s">
-        <v>44</v>
-      </c>
-      <c r="F44" s="81"/>
-      <c r="G44" s="80" t="s">
-        <v>45</v>
-      </c>
-      <c r="H44" s="81"/>
-      <c r="I44" s="80" t="s">
-        <v>46</v>
-      </c>
-      <c r="J44" s="81"/>
-      <c r="K44" s="82" t="s">
+      <c r="L44" s="80"/>
+      <c r="M44" s="81" t="s">
+        <v>80</v>
+      </c>
+      <c r="N44" s="82"/>
+      <c r="O44" s="82"/>
+      <c r="P44" s="82"/>
+      <c r="Q44" s="82"/>
+      <c r="R44" s="82"/>
+      <c r="S44" s="82"/>
+      <c r="T44" s="83"/>
+      <c r="U44" s="84" t="s">
+        <v>82</v>
+      </c>
+      <c r="V44" s="85"/>
+      <c r="W44" s="85"/>
+      <c r="X44" s="85"/>
+      <c r="Y44" s="85"/>
+      <c r="Z44" s="86"/>
+      <c r="AA44" s="84" t="s">
+        <v>83</v>
+      </c>
+      <c r="AB44" s="100"/>
+      <c r="AC44" s="100"/>
+      <c r="AD44" s="100"/>
+      <c r="AE44" s="100"/>
+      <c r="AF44" s="100"/>
+      <c r="AG44" s="101"/>
+      <c r="AH44" s="84" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI44" s="100"/>
+      <c r="AJ44" s="100"/>
+      <c r="AK44" s="100"/>
+      <c r="AL44" s="100"/>
+      <c r="AM44" s="100"/>
+      <c r="AN44" s="101"/>
+    </row>
+    <row r="45" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="L44" s="83"/>
-      <c r="M44" s="84" t="s">
-        <v>81</v>
-      </c>
-      <c r="N44" s="85"/>
-      <c r="O44" s="85"/>
-      <c r="P44" s="85"/>
-      <c r="Q44" s="85"/>
-      <c r="R44" s="85"/>
-      <c r="S44" s="85"/>
-      <c r="T44" s="86"/>
-      <c r="U44" s="87" t="s">
-        <v>83</v>
-      </c>
-      <c r="V44" s="88"/>
-      <c r="W44" s="88"/>
-      <c r="X44" s="88"/>
-      <c r="Y44" s="88"/>
-      <c r="Z44" s="89"/>
-      <c r="AA44" s="87" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB44" s="105"/>
-      <c r="AC44" s="105"/>
-      <c r="AD44" s="105"/>
-      <c r="AE44" s="105"/>
-      <c r="AF44" s="105"/>
-      <c r="AG44" s="106"/>
-      <c r="AH44" s="87" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI44" s="105"/>
-      <c r="AJ44" s="105"/>
-      <c r="AK44" s="105"/>
-      <c r="AL44" s="105"/>
-      <c r="AM44" s="105"/>
-      <c r="AN44" s="106"/>
-    </row>
-    <row r="45" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="103" t="s">
+      <c r="B45" s="24"/>
+      <c r="C45" s="58"/>
+      <c r="D45" s="60"/>
+      <c r="E45" s="58"/>
+      <c r="F45" s="60"/>
+      <c r="G45" s="58"/>
+      <c r="H45" s="60"/>
+      <c r="I45" s="58"/>
+      <c r="J45" s="60"/>
+      <c r="K45" s="58"/>
+      <c r="L45" s="60"/>
+      <c r="M45" s="58"/>
+      <c r="N45" s="59"/>
+      <c r="O45" s="59"/>
+      <c r="P45" s="59"/>
+      <c r="Q45" s="59"/>
+      <c r="R45" s="59"/>
+      <c r="S45" s="59"/>
+      <c r="T45" s="60"/>
+      <c r="U45" s="87"/>
+      <c r="V45" s="88"/>
+      <c r="W45" s="88"/>
+      <c r="X45" s="88"/>
+      <c r="Y45" s="88"/>
+      <c r="Z45" s="89"/>
+      <c r="AA45" s="55"/>
+      <c r="AB45" s="56"/>
+      <c r="AC45" s="56"/>
+      <c r="AD45" s="56"/>
+      <c r="AE45" s="56"/>
+      <c r="AF45" s="56"/>
+      <c r="AG45" s="57"/>
+      <c r="AH45" s="55"/>
+      <c r="AI45" s="56"/>
+      <c r="AJ45" s="56"/>
+      <c r="AK45" s="56"/>
+      <c r="AL45" s="56"/>
+      <c r="AM45" s="56"/>
+      <c r="AN45" s="57"/>
+    </row>
+    <row r="46" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="B45" s="104"/>
-      <c r="C45" s="61"/>
-      <c r="D45" s="63"/>
-      <c r="E45" s="61"/>
-      <c r="F45" s="63"/>
-      <c r="G45" s="61"/>
-      <c r="H45" s="63"/>
-      <c r="I45" s="61"/>
-      <c r="J45" s="63"/>
-      <c r="K45" s="61"/>
-      <c r="L45" s="63"/>
-      <c r="M45" s="61"/>
-      <c r="N45" s="62"/>
-      <c r="O45" s="62"/>
-      <c r="P45" s="62"/>
-      <c r="Q45" s="62"/>
-      <c r="R45" s="62"/>
-      <c r="S45" s="62"/>
-      <c r="T45" s="63"/>
-      <c r="U45" s="90"/>
-      <c r="V45" s="91"/>
-      <c r="W45" s="91"/>
-      <c r="X45" s="91"/>
-      <c r="Y45" s="91"/>
-      <c r="Z45" s="92"/>
-      <c r="AA45" s="58"/>
-      <c r="AB45" s="59"/>
-      <c r="AC45" s="59"/>
-      <c r="AD45" s="59"/>
-      <c r="AE45" s="59"/>
-      <c r="AF45" s="59"/>
-      <c r="AG45" s="60"/>
-      <c r="AH45" s="58"/>
-      <c r="AI45" s="59"/>
-      <c r="AJ45" s="59"/>
-      <c r="AK45" s="59"/>
-      <c r="AL45" s="59"/>
-      <c r="AM45" s="59"/>
-      <c r="AN45" s="60"/>
-    </row>
-    <row r="46" spans="1:40" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="103" t="s">
+      <c r="B46" s="24"/>
+      <c r="C46" s="58"/>
+      <c r="D46" s="60"/>
+      <c r="E46" s="58"/>
+      <c r="F46" s="60"/>
+      <c r="G46" s="58"/>
+      <c r="H46" s="60"/>
+      <c r="I46" s="58"/>
+      <c r="J46" s="60"/>
+      <c r="K46" s="58"/>
+      <c r="L46" s="60"/>
+      <c r="M46" s="58"/>
+      <c r="N46" s="59"/>
+      <c r="O46" s="59"/>
+      <c r="P46" s="59"/>
+      <c r="Q46" s="59"/>
+      <c r="R46" s="59"/>
+      <c r="S46" s="59"/>
+      <c r="T46" s="60"/>
+      <c r="U46" s="90" t="s">
         <v>74</v>
       </c>
-      <c r="B46" s="104"/>
-      <c r="C46" s="61"/>
-      <c r="D46" s="63"/>
-      <c r="E46" s="61"/>
-      <c r="F46" s="63"/>
-      <c r="G46" s="61"/>
-      <c r="H46" s="63"/>
-      <c r="I46" s="61"/>
-      <c r="J46" s="63"/>
-      <c r="K46" s="61"/>
-      <c r="L46" s="63"/>
-      <c r="M46" s="61"/>
-      <c r="N46" s="62"/>
-      <c r="O46" s="62"/>
-      <c r="P46" s="62"/>
-      <c r="Q46" s="62"/>
-      <c r="R46" s="62"/>
-      <c r="S46" s="62"/>
-      <c r="T46" s="63"/>
-      <c r="U46" s="93" t="s">
+      <c r="V46" s="91"/>
+      <c r="W46" s="91"/>
+      <c r="X46" s="91"/>
+      <c r="Y46" s="91"/>
+      <c r="Z46" s="92"/>
+      <c r="AA46" s="90" t="s">
         <v>75</v>
       </c>
-      <c r="V46" s="94"/>
-      <c r="W46" s="94"/>
-      <c r="X46" s="94"/>
-      <c r="Y46" s="94"/>
-      <c r="Z46" s="95"/>
-      <c r="AA46" s="93" t="s">
+      <c r="AB46" s="91"/>
+      <c r="AC46" s="91"/>
+      <c r="AD46" s="91"/>
+      <c r="AE46" s="91"/>
+      <c r="AF46" s="91"/>
+      <c r="AG46" s="92"/>
+      <c r="AH46" s="90" t="s">
         <v>76</v>
       </c>
-      <c r="AB46" s="94"/>
-      <c r="AC46" s="94"/>
-      <c r="AD46" s="94"/>
-      <c r="AE46" s="94"/>
-      <c r="AF46" s="94"/>
-      <c r="AG46" s="95"/>
-      <c r="AH46" s="93" t="s">
-        <v>77</v>
-      </c>
-      <c r="AI46" s="94"/>
-      <c r="AJ46" s="94"/>
-      <c r="AK46" s="94"/>
-      <c r="AL46" s="94"/>
-      <c r="AM46" s="94"/>
-      <c r="AN46" s="95"/>
+      <c r="AI46" s="91"/>
+      <c r="AJ46" s="91"/>
+      <c r="AK46" s="91"/>
+      <c r="AL46" s="91"/>
+      <c r="AM46" s="91"/>
+      <c r="AN46" s="92"/>
     </row>
     <row r="47" spans="1:40" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B47" s="20"/>
       <c r="C47" s="20"/>
@@ -4527,26 +4390,26 @@
       <c r="R47" s="20"/>
       <c r="S47" s="20"/>
       <c r="T47" s="21"/>
-      <c r="U47" s="90"/>
-      <c r="V47" s="91"/>
-      <c r="W47" s="91"/>
-      <c r="X47" s="91"/>
-      <c r="Y47" s="91"/>
-      <c r="Z47" s="92"/>
-      <c r="AA47" s="90"/>
-      <c r="AB47" s="91"/>
-      <c r="AC47" s="91"/>
-      <c r="AD47" s="91"/>
-      <c r="AE47" s="91"/>
-      <c r="AF47" s="91"/>
-      <c r="AG47" s="92"/>
-      <c r="AH47" s="90"/>
-      <c r="AI47" s="91"/>
-      <c r="AJ47" s="91"/>
-      <c r="AK47" s="91"/>
-      <c r="AL47" s="91"/>
-      <c r="AM47" s="91"/>
-      <c r="AN47" s="92"/>
+      <c r="U47" s="87"/>
+      <c r="V47" s="88"/>
+      <c r="W47" s="88"/>
+      <c r="X47" s="88"/>
+      <c r="Y47" s="88"/>
+      <c r="Z47" s="89"/>
+      <c r="AA47" s="87"/>
+      <c r="AB47" s="88"/>
+      <c r="AC47" s="88"/>
+      <c r="AD47" s="88"/>
+      <c r="AE47" s="88"/>
+      <c r="AF47" s="88"/>
+      <c r="AG47" s="89"/>
+      <c r="AH47" s="87"/>
+      <c r="AI47" s="88"/>
+      <c r="AJ47" s="88"/>
+      <c r="AK47" s="88"/>
+      <c r="AL47" s="88"/>
+      <c r="AM47" s="88"/>
+      <c r="AN47" s="89"/>
     </row>
   </sheetData>
   <mergeCells count="160">
@@ -4664,8 +4527,6 @@
     <mergeCell ref="V14:AB14"/>
     <mergeCell ref="B15:H15"/>
     <mergeCell ref="V15:AB15"/>
-    <mergeCell ref="I8:T8"/>
-    <mergeCell ref="U8:AF8"/>
     <mergeCell ref="AG8:AI8"/>
     <mergeCell ref="AK8:AM8"/>
     <mergeCell ref="A9:A10"/>
@@ -4688,6 +4549,8 @@
     <mergeCell ref="AG1:AN1"/>
     <mergeCell ref="AG2:AN2"/>
     <mergeCell ref="I3:AF4"/>
+    <mergeCell ref="I8:T8"/>
+    <mergeCell ref="U8:AF8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="AK3:AM3"/>
     <mergeCell ref="AG4:AI4"/>
@@ -4723,113 +4586,113 @@
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="3" spans="6:29" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F3" s="107" t="s">
+      <c r="F3" s="102" t="s">
         <v>0</v>
       </c>
-      <c r="G3" s="108"/>
-      <c r="H3" s="108"/>
-      <c r="I3" s="108"/>
-      <c r="J3" s="108"/>
-      <c r="K3" s="108"/>
-      <c r="L3" s="108"/>
-      <c r="M3" s="108"/>
-      <c r="N3" s="108"/>
-      <c r="O3" s="108"/>
-      <c r="P3" s="108"/>
-      <c r="Q3" s="108"/>
-      <c r="R3" s="108"/>
-      <c r="S3" s="108"/>
-      <c r="T3" s="108"/>
-      <c r="U3" s="108"/>
-      <c r="V3" s="108"/>
-      <c r="W3" s="108"/>
-      <c r="X3" s="108"/>
-      <c r="Y3" s="108"/>
-      <c r="Z3" s="108"/>
-      <c r="AA3" s="108"/>
-      <c r="AB3" s="108"/>
-      <c r="AC3" s="109"/>
+      <c r="G3" s="103"/>
+      <c r="H3" s="103"/>
+      <c r="I3" s="103"/>
+      <c r="J3" s="103"/>
+      <c r="K3" s="103"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="103"/>
+      <c r="N3" s="103"/>
+      <c r="O3" s="103"/>
+      <c r="P3" s="103"/>
+      <c r="Q3" s="103"/>
+      <c r="R3" s="103"/>
+      <c r="S3" s="103"/>
+      <c r="T3" s="103"/>
+      <c r="U3" s="103"/>
+      <c r="V3" s="103"/>
+      <c r="W3" s="103"/>
+      <c r="X3" s="103"/>
+      <c r="Y3" s="103"/>
+      <c r="Z3" s="103"/>
+      <c r="AA3" s="103"/>
+      <c r="AB3" s="103"/>
+      <c r="AC3" s="104"/>
     </row>
     <row r="4" spans="6:29" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F4" s="110"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="111"/>
-      <c r="L4" s="111"/>
-      <c r="M4" s="111"/>
-      <c r="N4" s="111"/>
-      <c r="O4" s="111"/>
-      <c r="P4" s="111"/>
-      <c r="Q4" s="111"/>
-      <c r="R4" s="111"/>
-      <c r="S4" s="111"/>
-      <c r="T4" s="111"/>
-      <c r="U4" s="111"/>
-      <c r="V4" s="111"/>
-      <c r="W4" s="111"/>
-      <c r="X4" s="111"/>
-      <c r="Y4" s="111"/>
-      <c r="Z4" s="111"/>
-      <c r="AA4" s="111"/>
-      <c r="AB4" s="111"/>
-      <c r="AC4" s="112"/>
+      <c r="F4" s="105"/>
+      <c r="G4" s="106"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
+      <c r="J4" s="106"/>
+      <c r="K4" s="106"/>
+      <c r="L4" s="106"/>
+      <c r="M4" s="106"/>
+      <c r="N4" s="106"/>
+      <c r="O4" s="106"/>
+      <c r="P4" s="106"/>
+      <c r="Q4" s="106"/>
+      <c r="R4" s="106"/>
+      <c r="S4" s="106"/>
+      <c r="T4" s="106"/>
+      <c r="U4" s="106"/>
+      <c r="V4" s="106"/>
+      <c r="W4" s="106"/>
+      <c r="X4" s="106"/>
+      <c r="Y4" s="106"/>
+      <c r="Z4" s="106"/>
+      <c r="AA4" s="106"/>
+      <c r="AB4" s="106"/>
+      <c r="AC4" s="107"/>
     </row>
     <row r="7" spans="6:29" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F7" s="96" t="s">
-        <v>79</v>
-      </c>
-      <c r="G7" s="97"/>
-      <c r="H7" s="97"/>
-      <c r="I7" s="97"/>
-      <c r="J7" s="97"/>
-      <c r="K7" s="97"/>
-      <c r="L7" s="97"/>
-      <c r="M7" s="97"/>
-      <c r="N7" s="97"/>
-      <c r="O7" s="97"/>
-      <c r="P7" s="97"/>
-      <c r="Q7" s="97"/>
-      <c r="R7" s="97"/>
-      <c r="S7" s="97"/>
-      <c r="T7" s="97"/>
-      <c r="U7" s="97"/>
-      <c r="V7" s="97"/>
-      <c r="W7" s="97"/>
-      <c r="X7" s="100" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y7" s="101"/>
-      <c r="Z7" s="101"/>
-      <c r="AA7" s="101"/>
-      <c r="AB7" s="101"/>
+      <c r="F7" s="93" t="s">
+        <v>78</v>
+      </c>
+      <c r="G7" s="94"/>
+      <c r="H7" s="94"/>
+      <c r="I7" s="94"/>
+      <c r="J7" s="94"/>
+      <c r="K7" s="94"/>
+      <c r="L7" s="94"/>
+      <c r="M7" s="94"/>
+      <c r="N7" s="94"/>
+      <c r="O7" s="94"/>
+      <c r="P7" s="94"/>
+      <c r="Q7" s="94"/>
+      <c r="R7" s="94"/>
+      <c r="S7" s="94"/>
+      <c r="T7" s="94"/>
+      <c r="U7" s="94"/>
+      <c r="V7" s="94"/>
+      <c r="W7" s="94"/>
+      <c r="X7" s="97" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y7" s="98"/>
+      <c r="Z7" s="98"/>
+      <c r="AA7" s="98"/>
+      <c r="AB7" s="98"/>
       <c r="AC7" s="26"/>
     </row>
     <row r="8" spans="6:29" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F8" s="98"/>
-      <c r="G8" s="99"/>
-      <c r="H8" s="99"/>
-      <c r="I8" s="99"/>
-      <c r="J8" s="99"/>
-      <c r="K8" s="99"/>
-      <c r="L8" s="99"/>
-      <c r="M8" s="99"/>
-      <c r="N8" s="99"/>
-      <c r="O8" s="99"/>
-      <c r="P8" s="99"/>
-      <c r="Q8" s="99"/>
-      <c r="R8" s="99"/>
-      <c r="S8" s="99"/>
-      <c r="T8" s="99"/>
-      <c r="U8" s="99"/>
-      <c r="V8" s="99"/>
-      <c r="W8" s="99"/>
-      <c r="X8" s="102"/>
-      <c r="Y8" s="102"/>
-      <c r="Z8" s="102"/>
-      <c r="AA8" s="102"/>
-      <c r="AB8" s="102"/>
+      <c r="F8" s="95"/>
+      <c r="G8" s="96"/>
+      <c r="H8" s="96"/>
+      <c r="I8" s="96"/>
+      <c r="J8" s="96"/>
+      <c r="K8" s="96"/>
+      <c r="L8" s="96"/>
+      <c r="M8" s="96"/>
+      <c r="N8" s="96"/>
+      <c r="O8" s="96"/>
+      <c r="P8" s="96"/>
+      <c r="Q8" s="96"/>
+      <c r="R8" s="96"/>
+      <c r="S8" s="96"/>
+      <c r="T8" s="96"/>
+      <c r="U8" s="96"/>
+      <c r="V8" s="96"/>
+      <c r="W8" s="96"/>
+      <c r="X8" s="99"/>
+      <c r="Y8" s="99"/>
+      <c r="Z8" s="99"/>
+      <c r="AA8" s="99"/>
+      <c r="AB8" s="99"/>
       <c r="AC8" s="28"/>
     </row>
   </sheetData>
